--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.28</v>
+        <v>3.62</v>
       </c>
       <c r="O19" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AA19" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
         <v>2.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>3.62</v>
+        <v>5.28</v>
       </c>
       <c r="O20" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.66</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="V20" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
         <v>2.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="M25" t="n">
         <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="M26" t="n">
         <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>3.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
         <v>2</v>
@@ -3801,7 +3801,7 @@
         <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2797,77 +2797,77 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
         <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
         <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="N16" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.66</v>
+        <v>3.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
-        <v>5.05</v>
+        <v>3.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.3</v>
+        <v>3.34</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="M19" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>5.28</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="P19" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="V19" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.14</v>
+        <v>2.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>5.28</v>
+        <v>3.62</v>
       </c>
       <c r="O21" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z21" t="n">
         <v>5</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AA21" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
         <v>2.34</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="M25" t="n">
         <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="M26" t="n">
         <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
         <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
         <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.81</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>4.25</v>
+        <v>6.2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.55</v>
+        <v>3.11</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="N14" t="n">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3280,10 +3280,10 @@
         <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="M25" t="n">
         <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="N20" t="n">
-        <v>5.28</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="V20" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.56</v>
+        <v>3.34</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="M21" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>5.28</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="P21" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="V21" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.14</v>
+        <v>2.34</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="M21" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="N21" t="n">
-        <v>5.28</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.56</v>
+        <v>3.34</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="N16" t="n">
-        <v>5.28</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.56</v>
+        <v>3.34</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>5.28</v>
       </c>
       <c r="O16" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.14</v>
+        <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.3</v>
+        <v>3.45</v>
       </c>
       <c r="M29" t="n">
-        <v>0.29</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>0.39</v>
+        <v>2.04</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="M18" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>5.28</v>
       </c>
       <c r="O18" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="P18" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="V18" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.14</v>
+        <v>2.34</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>5.8</v>
+        <v>3.84</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.62</v>
+        <v>5.28</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.66</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
         <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>3.84</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.62</v>
+        <v>5.28</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.66</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
         <v>2.34</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>5.8</v>
+        <v>3.84</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>5.8</v>
+        <v>3.84</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.45</v>
+        <v>0.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>0.29</v>
       </c>
       <c r="N29" t="n">
-        <v>2.04</v>
+        <v>0.39</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>5.28</v>
+        <v>3.62</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z16" t="n">
         <v>5</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AA16" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF16" t="n">
         <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>3.84</v>
+        <v>5.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.45</v>
+        <v>0.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>0.29</v>
       </c>
       <c r="N28" t="n">
-        <v>2.04</v>
+        <v>0.39</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="N17" t="n">
-        <v>5.28</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.56</v>
+        <v>3.34</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>5.8</v>
+        <v>3.84</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>3.84</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.3</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0.29</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>0.39</v>
+        <v>2.04</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="M17" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>5.28</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="P17" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.14</v>
+        <v>2.34</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>3.84</v>
+        <v>5.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.62</v>
+        <v>5.28</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.66</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
         <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>5.8</v>
+        <v>3.84</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.3</v>
+        <v>3.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0.29</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>0.39</v>
+        <v>2.04</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.45</v>
+        <v>0.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>0.29</v>
       </c>
       <c r="N29" t="n">
-        <v>2.04</v>
+        <v>0.39</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.45</v>
+        <v>0.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>0.29</v>
       </c>
       <c r="N27" t="n">
-        <v>2.04</v>
+        <v>0.39</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>3.84</v>
+        <v>5.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.3</v>
+        <v>3.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0.29</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>0.39</v>
+        <v>2.04</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="M15" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="M21" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="N21" t="n">
-        <v>5.28</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.56</v>
+        <v>3.34</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>5.8</v>
+        <v>3.84</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>3.84</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="M14" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="M21" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>5.28</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="P21" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="V21" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.14</v>
+        <v>2.34</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>3.84</v>
+        <v>5.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.56</v>
+        <v>2.17</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N23" t="n">
-        <v>5.8</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="O16" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.88</v>
+        <v>4.66</v>
       </c>
       <c r="R16" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="U16" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>3.4</v>
+        <v>5.05</v>
       </c>
       <c r="W16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.25</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="AH16" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.07</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>5.8</v>
+        <v>3.84</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,55 +3158,55 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.17</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>03:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -659,76 +659,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>46048.14583333334</v>
+        <v>46048.15277777778</v>
       </c>
     </row>
     <row r="3">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="N16" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.66</v>
+        <v>3.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
-        <v>5.05</v>
+        <v>3.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.3</v>
+        <v>3.34</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.28</v>
+        <v>3.62</v>
       </c>
       <c r="O19" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AA19" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
         <v>2.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,14 +3158,14 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.58</v>
+        <v>2.17</v>
       </c>
       <c r="M23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.25</v>
       </c>
-      <c r="N23" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,55 +3277,55 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.17</v>
       </c>
-      <c r="M24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="M15" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.84</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.21</v>
+        <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>3.54</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>0.08</v>
       </c>
       <c r="O2" t="n">
         <v>2.63</v>
@@ -704,10 +704,10 @@
         <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC2" t="n">
         <v>2.48</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="M14" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="N20" t="n">
-        <v>5.28</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="V20" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.56</v>
+        <v>3.34</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,55 +3039,55 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
         <v>2.17</v>
       </c>
-      <c r="M22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N23" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>5.8</v>
+        <v>3.84</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.45</v>
+        <v>0.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>0.29</v>
       </c>
       <c r="N27" t="n">
-        <v>2.04</v>
+        <v>0.39</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.06</v>
+        <v>2.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08</v>
+        <v>3.09</v>
       </c>
       <c r="O2" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="P2" t="n">
         <v>2.3</v>
@@ -683,7 +683,7 @@
         <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
         <v>1.52</v>
@@ -701,31 +701,31 @@
         <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE2" t="n">
         <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46048.15277777778</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.51388888889</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="M15" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.62</v>
+        <v>5.28</v>
       </c>
       <c r="O18" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.66</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="V18" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
         <v>2.34</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46048.375</v>
@@ -1382,40 +1382,40 @@
         <v>6.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" t="n">
         <v>1.91</v>
@@ -1424,22 +1424,22 @@
         <v>1.79</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46048.5</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1739,64 +1739,64 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -2096,40 +2096,40 @@
         <v>2.29</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA14" t="n">
         <v>1.93</v>
@@ -2138,22 +2138,22 @@
         <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.62</v>
+        <v>5.28</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.66</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
         <v>2.34</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>5.28</v>
+        <v>3.62</v>
       </c>
       <c r="O18" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z18" t="n">
         <v>5</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AA18" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
         <v>2.34</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,14 +3039,14 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.58</v>
+        <v>2.17</v>
       </c>
       <c r="M22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N22" t="n">
         <v>3.25</v>
       </c>
-      <c r="N22" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.84</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.84</v>
+        <v>5.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.25</v>
+        <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.09</v>
+        <v>0.08</v>
       </c>
       <c r="O2" t="n">
         <v>2.68</v>
@@ -686,10 +686,10 @@
         <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="V2" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="W2" t="n">
         <v>1.13</v>
@@ -704,22 +704,22 @@
         <v>4.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="AC2" t="n">
         <v>2.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AG2" t="n">
         <v>1.3</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="P10" t="n">
-        <v>2.41</v>
+        <v>2.13</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
+      <c r="AG10" t="n">
         <v>1.3</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="T11" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="V11" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="M14" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="N18" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.66</v>
+        <v>3.88</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="V18" t="n">
-        <v>5.05</v>
+        <v>3.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>3.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="M19" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>5.28</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="P19" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="V19" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.14</v>
+        <v>2.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.84</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>5.8</v>
+        <v>3.84</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O10" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="T10" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="V10" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>2.13</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2</v>
       </c>
-      <c r="R11" t="n">
+      <c r="AG11" t="n">
         <v>1.3</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="M15" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="N19" t="n">
-        <v>5.28</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.56</v>
+        <v>3.34</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>5.28</v>
       </c>
       <c r="O21" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.66</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="V21" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
         <v>2.34</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,55 +3039,55 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
         <v>2.17</v>
       </c>
-      <c r="M22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,14 +3158,14 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.58</v>
+        <v>2.17</v>
       </c>
       <c r="M23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.25</v>
       </c>
-      <c r="N23" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -677,10 +677,10 @@
         <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
         <v>2.4</v>
@@ -692,7 +692,7 @@
         <v>5.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
         <v>1.03</v>
@@ -722,7 +722,7 @@
         <v>2.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
         <v>1.65</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1391,13 +1391,13 @@
         <v>5.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
         <v>2.73</v>
       </c>
       <c r="T8" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
         <v>1.36</v>
@@ -1412,10 +1412,10 @@
         <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="n">
         <v>1.91</v>
@@ -1424,7 +1424,7 @@
         <v>1.79</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
         <v>1.26</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="M14" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.78</v>
+        <v>3.82</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
         <v>3.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
         <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2328,28 +2328,28 @@
         <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
         <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.66</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
         <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
         <v>1.53</v>
@@ -2358,40 +2358,40 @@
         <v>5.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB16" t="n">
         <v>2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
         <v>1.53</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2682,28 +2682,28 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="M19" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="P19" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="R19" t="n">
         <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T19" t="n">
         <v>1.8</v>
@@ -2712,31 +2712,31 @@
         <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AC19" t="n">
         <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AE19" t="n">
         <v>1.31</v>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.51</v>
+        <v>2.36</v>
       </c>
       <c r="M21" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>5.28</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="V21" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AD21" t="n">
         <v>1.67</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.34</v>
+        <v>2.86</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.43</v>
+        <v>1.55</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.58</v>
+        <v>2.17</v>
       </c>
       <c r="M22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N22" t="n">
         <v>3.25</v>
       </c>
-      <c r="N22" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.17</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3286,40 +3286,40 @@
         <v>3.84</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AA24" t="n">
         <v>2.05</v>
@@ -3328,22 +3328,22 @@
         <v>1.68</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3405,40 +3405,40 @@
         <v>2.94</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA25" t="n">
         <v>2.18</v>
@@ -3447,22 +3447,22 @@
         <v>1.61</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3524,40 +3524,40 @@
         <v>2.76</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA26" t="n">
         <v>2.5</v>
@@ -3566,22 +3566,22 @@
         <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3643,40 +3643,40 @@
         <v>2.04</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA27" t="n">
         <v>1.75</v>
@@ -3685,22 +3685,22 @@
         <v>1.95</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46048.71875</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1019,7 +1019,7 @@
         <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="N5" t="n">
         <v>4.55</v>
@@ -1061,7 +1061,7 @@
         <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB5" t="n">
         <v>2.1</v>
@@ -1073,13 +1073,13 @@
         <v>1.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF5" t="n">
         <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
         <v>2.17</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
         <v>3.71</v>
@@ -1510,13 +1510,13 @@
         <v>3.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
         <v>1.27</v>
@@ -1525,40 +1525,40 @@
         <v>9</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AD9" t="n">
         <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.51388888889</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6.25</v>
+        <v>4.47</v>
       </c>
       <c r="P10" t="n">
-        <v>2.41</v>
+        <v>2.13</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
+      <c r="AG10" t="n">
         <v>1.3</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>4.77</v>
       </c>
       <c r="P11" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="T11" t="n">
-        <v>2.72</v>
+        <v>2.41</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.60416666666</v>
@@ -1977,64 +1977,64 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.82</v>
+        <v>2.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T14" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="M15" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.78</v>
+        <v>3.82</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
         <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.52</v>
+        <v>2.03</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>4.65</v>
+        <v>2.68</v>
       </c>
       <c r="O17" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.43</v>
+        <v>5.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.43</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.29</v>
+        <v>1.72</v>
       </c>
       <c r="M18" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>8.85</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.5</v>
+        <v>4.05</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S18" t="n">
-        <v>3.84</v>
+        <v>4.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="V18" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.9</v>
+        <v>7.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.08</v>
+        <v>3.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.72</v>
+        <v>2.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V19" t="n">
         <v>3.75</v>
       </c>
-      <c r="O19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.13</v>
       </c>
-      <c r="S19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="Z19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.91</v>
       </c>
-      <c r="V19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD19" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.07</v>
+        <v>1.27</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.8</v>
+        <v>1.29</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.03</v>
+        <v>7.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="P20" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="V20" t="n">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.68</v>
+        <v>2.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>3.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.36</v>
+        <v>1.52</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P21" t="n">
         <v>2.5</v>
       </c>
-      <c r="O21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.32</v>
-      </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="V21" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.86</v>
+        <v>2.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.55</v>
+        <v>2.43</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.84</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.22</v>
+        <v>2.86</v>
       </c>
       <c r="T22" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="U22" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="V22" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.75</v>
+        <v>3.71</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.58</v>
+        <v>2.17</v>
       </c>
       <c r="M23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.25</v>
       </c>
-      <c r="N23" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O23" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.14</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.22</v>
       </c>
       <c r="T23" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.9</v>
+        <v>2.51</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,37 +3277,37 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.84</v>
+        <v>5.8</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.15</v>
+        <v>6.14</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.86</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="W24" t="n">
         <v>1.03</v>
@@ -3316,34 +3316,34 @@
         <v>1.06</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z24" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="AH24" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.45</v>
+        <v>0.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>0.29</v>
       </c>
       <c r="N27" t="n">
-        <v>2.04</v>
+        <v>0.39</v>
       </c>
       <c r="O27" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>2.57</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V27" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.53</v>
-      </c>
-      <c r="V27" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.3</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0.29</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>0.39</v>
+        <v>2.04</v>
       </c>
       <c r="O28" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>2.57</v>
+        <v>3.2</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.74</v>
+        <v>2.54</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.53</v>
+        <v>1.36</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07000000000000001</v>
+        <v>4.62</v>
       </c>
       <c r="N30" t="n">
-        <v>0.05</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="O30" t="n">
         <v>1.85</v>
@@ -4036,16 +4036,16 @@
         <v>3.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
         <v>3.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE30" t="n">
         <v>2.28</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46048.15277777778</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="R12" t="n">
         <v>1.15</v>
@@ -1873,16 +1873,16 @@
         <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="U12" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="V12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -1891,31 +1891,31 @@
         <v>1.06</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AB12" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.15</v>
@@ -1992,16 +1992,16 @@
         <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
@@ -2010,31 +2010,31 @@
         <v>1.06</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>4.65</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.2</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.92</v>
+        <v>2.43</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.72</v>
+        <v>2.8</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V18" t="n">
         <v>3.75</v>
       </c>
-      <c r="O18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.13</v>
       </c>
-      <c r="S18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="Z18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.91</v>
       </c>
-      <c r="V18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD18" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.07</v>
+        <v>1.27</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.11</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="P19" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.58</v>
+        <v>4.05</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>3.68</v>
+        <v>4.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.27</v>
+        <v>2.07</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>4.65</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="P21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q21" t="n">
-        <v>5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.43</v>
+        <v>1.92</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>2.86</v>
+        <v>2.22</v>
       </c>
       <c r="T22" t="n">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.23</v>
+        <v>2.51</v>
       </c>
       <c r="AA22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE22" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.84</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.22</v>
+        <v>2.86</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.75</v>
+        <v>3.71</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>0.29</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.39</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>4.85</v>
       </c>
       <c r="R27" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="S27" t="n">
-        <v>2.57</v>
+        <v>2.32</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="U27" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="V27" t="n">
-        <v>8.1</v>
+        <v>11</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF27" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.87</v>
       </c>
       <c r="AG27" t="n">
         <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.45</v>
+        <v>0.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>0.29</v>
       </c>
       <c r="N28" t="n">
-        <v>2.04</v>
+        <v>0.39</v>
       </c>
       <c r="O28" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>2.57</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V28" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.53</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>3.45</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>3.8</v>
+        <v>2.04</v>
       </c>
       <c r="O29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q29" t="n">
         <v>2.7</v>
       </c>
-      <c r="P29" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.85</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>2.32</v>
+        <v>3.2</v>
       </c>
       <c r="T29" t="n">
-        <v>4.05</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="V29" t="n">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.66</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.75</v>
+        <v>2.54</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="N5" t="n">
         <v>4.55</v>
@@ -1040,7 +1040,7 @@
         <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="U5" t="n">
         <v>1.44</v>
@@ -1055,7 +1055,7 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
         <v>4</v>
@@ -1064,10 +1064,10 @@
         <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="AD5" t="n">
         <v>1.38</v>
@@ -1079,10 +1079,10 @@
         <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46048.375</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O10" t="n">
-        <v>4.47</v>
+        <v>4.77</v>
       </c>
       <c r="P10" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="T10" t="n">
-        <v>2.72</v>
+        <v>2.41</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.77</v>
+        <v>4.47</v>
       </c>
       <c r="P11" t="n">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.3</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="M14" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.78</v>
+        <v>3.82</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.82</v>
+        <v>2.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
         <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.52</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>4.65</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.43</v>
+        <v>5.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.43</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="M17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N17" t="n">
         <v>3.75</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.68</v>
-      </c>
       <c r="O17" t="n">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="P17" t="n">
-        <v>2.32</v>
+        <v>2.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="S17" t="n">
-        <v>3.68</v>
+        <v>4.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="V17" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.75</v>
+        <v>7.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.8</v>
+        <v>1.29</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.11</v>
+        <v>7.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.58</v>
+        <v>6.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.87</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.27</v>
+        <v>3.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.72</v>
+        <v>2.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V19" t="n">
         <v>3.75</v>
       </c>
-      <c r="O19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.13</v>
       </c>
-      <c r="S19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="Z19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.91</v>
       </c>
-      <c r="V19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD19" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.07</v>
+        <v>1.27</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="M20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q20" t="n">
         <v>5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6.5</v>
       </c>
       <c r="R20" t="n">
         <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="V20" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.9</v>
+        <v>5.43</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.95</v>
+        <v>2.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.3</v>
+        <v>2.43</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA22" t="n">
         <v>2.17</v>
       </c>
-      <c r="M22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="AB22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC22" t="n">
         <v>3.5</v>
       </c>
-      <c r="U22" t="n">
+      <c r="AD22" t="n">
         <v>1.22</v>
       </c>
-      <c r="V22" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH22" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N23" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.86</v>
+        <v>2.22</v>
       </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.23</v>
+        <v>2.51</v>
       </c>
       <c r="AA23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,37 +3277,37 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>5.8</v>
+        <v>3.84</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.14</v>
+        <v>4.15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.47</v>
+        <v>2.86</v>
       </c>
       <c r="T24" t="n">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.03</v>
@@ -3316,34 +3316,34 @@
         <v>1.06</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH24" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46048.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.77</v>
+        <v>4.47</v>
       </c>
       <c r="P10" t="n">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.3</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O11" t="n">
-        <v>4.47</v>
+        <v>4.77</v>
       </c>
       <c r="P11" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="T11" t="n">
-        <v>2.72</v>
+        <v>2.41</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -2096,13 +2096,13 @@
         <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
@@ -2111,10 +2111,10 @@
         <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V14" t="n">
         <v>7.8</v>
@@ -2123,13 +2123,13 @@
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA14" t="n">
         <v>2.05</v>
@@ -2138,13 +2138,13 @@
         <v>1.68</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
         <v>1.91</v>
@@ -2221,19 +2221,19 @@
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
         <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>2.87</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
         <v>7.2</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>2.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>2.11</v>
       </c>
       <c r="O16" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="R16" t="n">
         <v>1.21</v>
@@ -2349,13 +2349,13 @@
         <v>3.68</v>
       </c>
       <c r="T16" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="U16" t="n">
         <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>4.45</v>
+        <v>3.75</v>
       </c>
       <c r="W16" t="n">
         <v>1.14</v>
@@ -2364,34 +2364,34 @@
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
         <v>2.63</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="n">
         <v>1.36</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="P17" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.05</v>
+        <v>6.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.3</v>
+        <v>5.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.07</v>
+        <v>3.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.29</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>7.5</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
-        <v>1.71</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="T18" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
         <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.58</v>
+        <v>4.6</v>
       </c>
       <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.21</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.27</v>
+        <v>1.92</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.82</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.25</v>
+        <v>7.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.41</v>
+        <v>3.14</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,37 +3039,37 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>5.8</v>
+        <v>3.84</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="P22" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.14</v>
+        <v>4.15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="W22" t="n">
         <v>1.03</v>
@@ -3078,34 +3078,34 @@
         <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.9</v>
+        <v>3.23</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.17</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="AB23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC23" t="n">
         <v>3.5</v>
       </c>
-      <c r="U23" t="n">
+      <c r="AD23" t="n">
         <v>1.22</v>
       </c>
-      <c r="V23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH23" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
-        <v>2.86</v>
+        <v>2.35</v>
       </c>
       <c r="T24" t="n">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="V24" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.23</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE24" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O25" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
         <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U25" t="n">
         <v>1.29</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="AD25" t="n">
         <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="O26" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="P26" t="n">
         <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="R26" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U26" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V26" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AD26" t="n">
         <v>1.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.1</v>
+        <v>3.45</v>
       </c>
       <c r="M27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S27" t="n">
         <v>3.1</v>
       </c>
-      <c r="N27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.32</v>
-      </c>
       <c r="T27" t="n">
-        <v>4.05</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="V27" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.66</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3762,40 +3762,40 @@
         <v>0.39</v>
       </c>
       <c r="O28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>2.3</v>
@@ -3804,22 +3804,22 @@
         <v>1.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.04</v>
+        <v>3.8</v>
       </c>
       <c r="O29" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="P29" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.7</v>
+        <v>4.85</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="S29" t="n">
-        <v>3.2</v>
+        <v>2.32</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>4.05</v>
       </c>
       <c r="U29" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="V29" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>2.76</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.54</v>
+        <v>5.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.36</v>
+        <v>0.53</v>
       </c>
       <c r="M30" t="n">
-        <v>4.62</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>8.220000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="O30" t="n">
         <v>1.85</v>
@@ -4018,7 +4018,7 @@
         <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
         <v>6.8</v>
@@ -4036,10 +4036,10 @@
         <v>3.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
         <v>3.4</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.06</v>
+        <v>2.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46048.15277777778</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="P8" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.75</v>
+        <v>6.63</v>
       </c>
       <c r="R8" t="n">
         <v>1.39</v>
@@ -1415,22 +1415,22 @@
         <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AD8" t="n">
         <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
         <v>1.75</v>
@@ -1439,7 +1439,7 @@
         <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46048.5</v>
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.75</v>
+        <v>4.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
         <v>1.27</v>
@@ -1531,34 +1531,34 @@
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA9" t="n">
         <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AG9" t="n">
         <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.51388888889</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O10" t="n">
-        <v>4.47</v>
+        <v>4.77</v>
       </c>
       <c r="P10" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="T10" t="n">
-        <v>2.72</v>
+        <v>2.41</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.77</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
         <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="P12" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>5.51</v>
       </c>
       <c r="R12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
         <v>1.74</v>
       </c>
       <c r="V12" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.06</v>
       </c>
-      <c r="Z12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH12" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="P13" t="n">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.5</v>
+        <v>7.14</v>
       </c>
       <c r="R13" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="U13" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="V13" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AG13" t="n">
         <v>1.02</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.8</v>
+        <v>4.85</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,43 +2087,43 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>3.3</v>
       </c>
       <c r="M14" t="n">
         <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T14" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
@@ -2132,28 +2132,28 @@
         <v>3.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>2.91</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
         <v>2.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
         <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
         <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.58</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.21</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>1.92</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>2.8</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>7.5</v>
+        <v>2.11</v>
       </c>
       <c r="O17" t="n">
-        <v>1.71</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.5</v>
+        <v>2.58</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="T17" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.3</v>
+        <v>1.27</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>1.29</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>7.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
         <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>2.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.25</v>
+        <v>7.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.41</v>
+        <v>3.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.52</v>
+        <v>2.03</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>4.65</v>
+        <v>2.68</v>
       </c>
       <c r="O20" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="T20" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="U20" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V20" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.43</v>
+        <v>5.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.43</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>4.65</v>
       </c>
       <c r="O21" t="n">
         <v>2.08</v>
       </c>
       <c r="P21" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="V21" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.3</v>
+        <v>5.43</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="N22" t="n">
-        <v>3.84</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="P22" t="n">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.15</v>
+        <v>4.46</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.23</v>
+        <v>2.4</v>
       </c>
       <c r="AA22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE22" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N23" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.22</v>
+        <v>2.57</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.03</v>
+        <v>4.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="W23" t="n">
         <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="M24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
         <v>2.9</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="AA24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC24" t="n">
         <v>3.5</v>
       </c>
-      <c r="U24" t="n">
+      <c r="AD24" t="n">
         <v>1.22</v>
       </c>
-      <c r="V24" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH24" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.04</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.7</v>
+        <v>4.85</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>4.05</v>
       </c>
       <c r="U27" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="V27" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>2.76</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.6</v>
+        <v>5.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>3.45</v>
       </c>
       <c r="M29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.1</v>
       </c>
-      <c r="N29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.32</v>
-      </c>
       <c r="T29" t="n">
-        <v>4.05</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="V29" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.66</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
         <v>3.87</v>
@@ -1025,13 +1025,13 @@
         <v>4.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="R5" t="n">
         <v>1.29</v>
@@ -1040,22 +1040,22 @@
         <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
         <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
         <v>4</v>
@@ -1064,10 +1064,10 @@
         <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
         <v>1.38</v>
@@ -1079,10 +1079,10 @@
         <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46048.375</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M10" t="n">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="N10" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="O10" t="n">
-        <v>4.77</v>
+        <v>6.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="R10" t="n">
         <v>1.3</v>
@@ -1641,43 +1641,43 @@
         <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W10" t="n">
         <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.2</v>
+        <v>4.41</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB10" t="n">
         <v>2.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>8.130000000000001</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.51</v>
+        <v>7.14</v>
       </c>
       <c r="R12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="U12" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="V12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="W12" t="n">
         <v>1.19</v>
@@ -1888,34 +1888,34 @@
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.45</v>
+        <v>4.85</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,37 +1968,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="P13" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.14</v>
+        <v>5.51</v>
       </c>
       <c r="R13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="V13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="W13" t="n">
         <v>1.19</v>
@@ -2007,34 +2007,34 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.85</v>
+        <v>3.45</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,43 +2087,43 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>2.91</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
         <v>2.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
@@ -2132,28 +2132,28 @@
         <v>3.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
         <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,43 +2206,43 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2.8</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
         <v>2.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
@@ -2251,28 +2251,28 @@
         <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="AB15" t="n">
         <v>1.73</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
         <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.82</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.25</v>
+        <v>7.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.41</v>
+        <v>3.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.8</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.34</v>
-      </c>
       <c r="Q17" t="n">
-        <v>2.58</v>
+        <v>6.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="T17" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.27</v>
+        <v>3.45</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.9</v>
+        <v>4.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.3</v>
+        <v>1.92</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>3.75</v>
+        <v>2.68</v>
       </c>
       <c r="O19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.08</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.8</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="V19" t="n">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="W19" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.3</v>
+        <v>5.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,22 +2801,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.03</v>
+        <v>2.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.8</v>
+        <v>3.52</v>
       </c>
       <c r="P20" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="R20" t="n">
         <v>1.21</v>
@@ -2825,13 +2825,13 @@
         <v>3.68</v>
       </c>
       <c r="T20" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="U20" t="n">
         <v>1.68</v>
       </c>
       <c r="V20" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="W20" t="n">
         <v>1.14</v>
@@ -2840,34 +2840,34 @@
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB20" t="n">
         <v>2.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE20" t="n">
         <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2968,7 +2968,7 @@
         <v>1.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AC21" t="n">
         <v>2.2</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="N25" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="R25" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U25" t="n">
         <v>1.29</v>
       </c>
       <c r="V25" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
         <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="P26" t="n">
         <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>3.28</v>
+        <v>3.64</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
         <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AD26" t="n">
         <v>1.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.1</v>
+        <v>2.68</v>
       </c>
       <c r="M27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S27" t="n">
         <v>3.1</v>
       </c>
-      <c r="N27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.32</v>
-      </c>
       <c r="T27" t="n">
-        <v>4.05</v>
+        <v>2.44</v>
       </c>
       <c r="U27" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="V27" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.66</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF27" t="n">
         <v>2.42</v>
       </c>
-      <c r="AA27" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>0.29</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.39</v>
+        <v>2.97</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="N29" t="n">
-        <v>2.04</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>4.05</v>
       </c>
       <c r="U29" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="V29" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>2.72</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>1.39</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.6</v>
+        <v>5.65</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.53</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07000000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.05</v>
+        <v>8.5</v>
       </c>
       <c r="O30" t="n">
         <v>1.85</v>
       </c>
       <c r="P30" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="Q30" t="n">
         <v>7.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="T30" t="n">
         <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
         <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="AF30" t="n">
         <v>1.62</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46048.71875</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.01</v>
+        <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>0.08</v>
       </c>
       <c r="O2" t="n">
         <v>2.63</v>
@@ -704,16 +704,16 @@
         <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
         <v>1.53</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
         <v>6.4</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.87</v>
       </c>
-      <c r="R10" t="n">
+      <c r="AB10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.3</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>4.41</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="P12" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.14</v>
+        <v>5.51</v>
       </c>
       <c r="R12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="V12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="W12" t="n">
         <v>1.19</v>
@@ -1888,34 +1888,34 @@
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.85</v>
+        <v>3.45</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,37 +1968,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>8.130000000000001</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="P13" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.51</v>
+        <v>7.14</v>
       </c>
       <c r="R13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="U13" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="V13" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="W13" t="n">
         <v>1.19</v>
@@ -2007,34 +2007,34 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.45</v>
+        <v>4.85</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="P16" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.05</v>
+        <v>6.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>4.8</v>
+        <v>3.82</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="U16" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.3</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD16" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.07</v>
+        <v>3.45</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>2.8</v>
       </c>
       <c r="M17" t="n">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.67</v>
+        <v>3.52</v>
       </c>
       <c r="P17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.45</v>
+        <v>1.33</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="O20" t="n">
-        <v>3.52</v>
+        <v>2.08</v>
       </c>
       <c r="P20" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.58</v>
+        <v>4.05</v>
       </c>
       <c r="R20" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>3.68</v>
+        <v>4.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="V20" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="M22" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z22" t="n">
         <v>2.9</v>
       </c>
-      <c r="P22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="AA22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC22" t="n">
         <v>3.5</v>
       </c>
-      <c r="U22" t="n">
+      <c r="AD22" t="n">
         <v>1.22</v>
       </c>
-      <c r="V22" t="n">
-        <v>10</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AE22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH22" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.33</v>
+        <v>2.76</v>
       </c>
       <c r="N23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.5</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.99</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.03</v>
+        <v>4.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3515,58 +3515,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="O26" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="R26" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
         <v>3.64</v>
       </c>
       <c r="U26" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AA26" t="n">
         <v>2.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AD26" t="n">
         <v>1.17</v>
@@ -3575,13 +3575,13 @@
         <v>2.05</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.68</v>
+        <v>2.02</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.35</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.79</v>
+        <v>4.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="T27" t="n">
-        <v>2.44</v>
+        <v>3.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="V27" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.08</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.67</v>
+        <v>2.72</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.6</v>
+        <v>5.65</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>2.29</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.42</v>
+        <v>1.6</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>2.99</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.97</v>
+        <v>2.25</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="R28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.5</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.4</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>2.97</v>
       </c>
       <c r="O29" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="T29" t="n">
-        <v>4.05</v>
+        <v>2.88</v>
       </c>
       <c r="U29" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.65</v>
+        <v>4.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
         <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3994,13 +3994,13 @@
         <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="N30" t="n">
-        <v>8.5</v>
+        <v>7.75</v>
       </c>
       <c r="O30" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="P30" t="n">
         <v>2.21</v>
@@ -4036,10 +4036,10 @@
         <v>2.99</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
         <v>3.72</v>
@@ -4054,10 +4054,10 @@
         <v>1.62</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46048.71875</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O10" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.6</v>
+        <v>4.41</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
         <v>6.4</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.87</v>
       </c>
-      <c r="R11" t="n">
+      <c r="AB11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.3</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,43 +2087,43 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2.8</v>
       </c>
-      <c r="O14" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T14" t="n">
         <v>2.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
@@ -2132,28 +2132,28 @@
         <v>3.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="AB14" t="n">
         <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.3</v>
+        <v>2.08</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
         <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
         <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="P16" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Q16" t="n">
         <v>6.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V16" t="n">
         <v>4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z16" t="n">
         <v>6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AD16" t="n">
         <v>1.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>4.65</v>
       </c>
       <c r="O17" t="n">
-        <v>3.52</v>
+        <v>2.08</v>
       </c>
       <c r="P17" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.58</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.68</v>
       </c>
-      <c r="V17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.33</v>
+        <v>2.43</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>2.73</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O18" t="n">
         <v>3.2</v>
       </c>
-      <c r="O18" t="n">
-        <v>2.25</v>
-      </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="V18" t="n">
-        <v>5.05</v>
+        <v>3.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.25</v>
+        <v>5.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.92</v>
+        <v>1.35</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.21</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="P20" t="n">
-        <v>2.82</v>
+        <v>2.36</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.05</v>
+        <v>3.07</v>
       </c>
       <c r="R20" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="U20" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="V20" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="W20" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.3</v>
+        <v>5.93</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="M21" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>4.65</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
         <v>2.08</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.43</v>
+        <v>7.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.35</v>
+        <v>3.14</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI32"/>
+  <dimension ref="A1:AI33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,37 +671,37 @@
         <v>2.63</v>
       </c>
       <c r="P2" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
         <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="U2" t="n">
         <v>1.51</v>
       </c>
       <c r="V2" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
         <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>4.44</v>
       </c>
       <c r="AA2" t="n">
         <v>1.63</v>
@@ -710,16 +710,16 @@
         <v>2.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE2" t="n">
         <v>1.53</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AG2" t="n">
         <v>1.25</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1373,37 +1373,37 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.63</v>
+        <v>5.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="T8" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
@@ -1412,25 +1412,25 @@
         <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
         <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AF8" t="n">
         <v>1.75</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,80 +1488,80 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.64</v>
+        <v>4.55</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>2.44</v>
+        <v>2.91</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="V9" t="n">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.74</v>
+        <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46048.51388888889</v>
+        <v>46048.5</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.39</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
-        <v>6.4</v>
+        <v>2.69</v>
       </c>
       <c r="P10" t="n">
-        <v>2.41</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.87</v>
+        <v>4.64</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>3.22</v>
+        <v>2.44</v>
       </c>
       <c r="T10" t="n">
-        <v>2.41</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.41</v>
+        <v>2.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.09</v>
+        <v>1.68</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46048.58333333334</v>
+        <v>46048.51388888889</v>
       </c>
     </row>
     <row r="11">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.21</v>
       </c>
-      <c r="M12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AH12" t="n">
         <v>1.09</v>
       </c>
-      <c r="Z12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AI12" s="3" t="n">
-        <v>46048.60416666666</v>
+        <v>46048.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.3</v>
+        <v>1.21</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>6.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>1.61</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>5.51</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.98</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="V14" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>2.83</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.28</v>
+        <v>1.96</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>3.45</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46048.625</v>
+        <v>46048.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="T15" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
         <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.02</v>
       </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
         <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
         <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.33</v>
       </c>
-      <c r="M16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.75</v>
-      </c>
       <c r="V16" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.33</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.83</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.87</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.18</v>
+        <v>1.58</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46048.66666666666</v>
+        <v>46048.625</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>4.65</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.43</v>
+        <v>1.92</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.73</v>
+        <v>1.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.03</v>
+        <v>4.65</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="P18" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="V18" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.7</v>
+        <v>5.43</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.35</v>
+        <v>2.43</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>2.73</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O19" t="n">
         <v>3.2</v>
       </c>
-      <c r="O19" t="n">
-        <v>2.25</v>
-      </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="V19" t="n">
-        <v>5.05</v>
+        <v>3.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.25</v>
+        <v>5.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.92</v>
+        <v>1.35</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="P20" t="n">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.07</v>
+        <v>6.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V20" t="n">
         <v>4</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4.33</v>
-      </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>3.18</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.82</v>
+        <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.05</v>
+        <v>3.07</v>
       </c>
       <c r="R21" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="V21" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.3</v>
+        <v>5.93</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S22" t="n">
         <v>4.8</v>
       </c>
-      <c r="O22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.68</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.92</v>
+        <v>1.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.91</v>
       </c>
       <c r="V22" t="n">
-        <v>7.2</v>
+        <v>3.5</v>
       </c>
       <c r="W22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.03</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z22" t="n">
-        <v>2.9</v>
+        <v>7.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.97</v>
+        <v>1.31</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.69</v>
+        <v>3.14</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46048.6875</v>
+        <v>46048.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3158,43 +3158,43 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="M23" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>2.9</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S23" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
         <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y23" t="n">
         <v>1.5</v>
@@ -3203,16 +3203,16 @@
         <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
         <v>2.05</v>
@@ -3277,31 +3277,31 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="O24" t="n">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
         <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="U24" t="n">
         <v>1.34</v>
@@ -3310,40 +3310,40 @@
         <v>7.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,76 +3396,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.55</v>
+        <v>1.58</v>
       </c>
       <c r="M25" t="n">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>5.8</v>
       </c>
       <c r="O25" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.32</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="T25" t="n">
-        <v>3.28</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC25" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.46</v>
+        <v>2.05</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46048.69791666666</v>
+        <v>46048.6875</v>
       </c>
     </row>
     <row r="26">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="O26" t="n">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T26" t="n">
-        <v>3.64</v>
+        <v>3.31</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V26" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.85</v>
+        <v>4.2</v>
       </c>
       <c r="AD26" t="n">
         <v>1.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,76 +3634,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>2.76</v>
       </c>
       <c r="O27" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="U27" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="V27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W27" t="n">
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.65</v>
+        <v>4.85</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46048.70833333334</v>
+        <v>46048.69791666666</v>
       </c>
     </row>
     <row r="28">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.99</v>
+        <v>0.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>0.29</v>
       </c>
       <c r="N28" t="n">
-        <v>2.25</v>
+        <v>0.39</v>
       </c>
       <c r="O28" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="T28" t="n">
-        <v>2.41</v>
+        <v>3.24</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="W28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.08</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.22</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.51</v>
+        <v>4.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.4</v>
+        <v>3.45</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>2.97</v>
+        <v>2.04</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="R29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.5</v>
       </c>
-      <c r="S29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V29" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.84</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.2</v>
+        <v>2.51</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,76 +3991,76 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V30" t="n">
+        <v>10</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.4</v>
       </c>
-      <c r="M30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC30" t="n">
-        <v>3.72</v>
+        <v>5.65</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.9</v>
+        <v>1.73</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46048.71875</v>
+        <v>46048.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,76 +4110,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46048.79166666666</v>
+        <v>46048.71875</v>
       </c>
     </row>
     <row r="32">
@@ -4188,116 +4188,235 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Dunbeholden</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Harbour View</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="n">
+        <v>46048.79166666666</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Racing United</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Portmore United</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="3" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3" t="n">
         <v>46048.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46048.15277777778</v>
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>3.87</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
         <v>4.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="P5" t="n">
         <v>2.3</v>
@@ -1040,7 +1040,7 @@
         <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="U5" t="n">
         <v>1.5</v>
@@ -1049,7 +1049,7 @@
         <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
@@ -1058,16 +1058,16 @@
         <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD5" t="n">
         <v>1.38</v>
@@ -1076,13 +1076,13 @@
         <v>1.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
         <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.48</v>
+        <v>2.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46048.375</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>4.25</v>
+        <v>3.81</v>
       </c>
       <c r="O9" t="n">
-        <v>2.78</v>
+        <v>4.72</v>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.55</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>2.91</v>
+        <v>2.54</v>
       </c>
       <c r="T9" t="n">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.68</v>
+        <v>3.89</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>1.23</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.5</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.64</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
         <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AA10" t="n">
         <v>2.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.51388888889</v>
@@ -1742,16 +1742,16 @@
         <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
         <v>2.62</v>
@@ -1766,31 +1766,31 @@
         <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
         <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
         <v>1.3</v>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="M12" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="N12" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
@@ -1873,28 +1873,28 @@
         <v>3.22</v>
       </c>
       <c r="T12" t="n">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="U12" t="n">
         <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
         <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.41</v>
+        <v>4.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB12" t="n">
         <v>2.15</v>
@@ -1903,19 +1903,19 @@
         <v>2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1977,13 +1977,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.14</v>
+        <v>10.6</v>
       </c>
       <c r="R13" t="n">
         <v>1.13</v>
@@ -1992,49 +1992,49 @@
         <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V13" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="W13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M14" t="n">
         <v>6.3</v>
       </c>
       <c r="N14" t="n">
-        <v>8.130000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="P14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.51</v>
+        <v>6.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
         <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z14" t="n">
         <v>6.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="M15" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>2.88</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
         <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O16" t="n">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="T16" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.02</v>
       </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
         <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD16" t="n">
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.625</v>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
         <v>3.6</v>
@@ -2459,55 +2459,55 @@
         <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V17" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
         <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB17" t="n">
         <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
         <v>1.92</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>4.65</v>
+        <v>8.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U18" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="V18" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.43</v>
+        <v>6.05</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2682,19 +2682,19 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.73</v>
+        <v>3.01</v>
       </c>
       <c r="M19" t="n">
         <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="O19" t="n">
         <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
         <v>2.5</v>
@@ -2706,10 +2706,10 @@
         <v>3.68</v>
       </c>
       <c r="T19" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
         <v>3.75</v>
@@ -2730,16 +2730,16 @@
         <v>1.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AC19" t="n">
         <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF19" t="n">
         <v>2.8</v>
@@ -2748,7 +2748,7 @@
         <v>1.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,22 +2801,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>8.5</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.5</v>
+        <v>3.77</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
@@ -2825,49 +2825,49 @@
         <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="U20" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V20" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.83</v>
+        <v>3.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.18</v>
+        <v>2.94</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.18</v>
+        <v>1.85</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>4.65</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="P21" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.07</v>
+        <v>4.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
         <v>4.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.93</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.53</v>
+        <v>2.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.72</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.91</v>
-      </c>
       <c r="V22" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.3</v>
+        <v>5.93</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.17</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="AB23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE23" t="n">
+      <c r="AF23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH23" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R25" t="n">
         <v>1.58</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="S25" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="V25" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.75</v>
+        <v>4.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46048.6875</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.3</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
-        <v>0.29</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.39</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -3783,7 +3783,7 @@
         <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W28" t="n">
         <v>1.05</v>
@@ -3798,13 +3798,13 @@
         <v>2.84</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="AD28" t="n">
         <v>1.22</v>
@@ -3819,7 +3819,7 @@
         <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="M30" t="n">
         <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
         <v>2.7</v>
@@ -4018,10 +4018,10 @@
         <v>3.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W30" t="n">
         <v>1</v>
@@ -4033,7 +4033,7 @@
         <v>1.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AA30" t="n">
         <v>2.72</v>
@@ -4048,7 +4048,7 @@
         <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AF30" t="n">
         <v>1.6</v>
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.53</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
-        <v>0.07000000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.05</v>
+        <v>7.75</v>
       </c>
       <c r="O31" t="n">
         <v>1.92</v>
@@ -4143,7 +4143,7 @@
         <v>6.95</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
         <v>1.02</v>
@@ -4155,28 +4155,28 @@
         <v>3.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
         <v>3.72</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
         <v>2.46</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46048.71875</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI33"/>
+  <dimension ref="A1:AI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="N5" t="n">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
         <v>2.1</v>
@@ -1040,7 +1040,7 @@
         <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="U5" t="n">
         <v>1.5</v>
@@ -1058,19 +1058,19 @@
         <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
         <v>2.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
         <v>1.7</v>
@@ -1082,7 +1082,7 @@
         <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46048.375</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,80 +1488,80 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.81</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>4.72</v>
+        <v>2.7</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.64</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="T9" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.89</v>
+        <v>4.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
         <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46048.5</v>
+        <v>46048.51388888889</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="P10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V10" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46048.51388888889</v>
+        <v>46048.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>6.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.46</v>
+        <v>1.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.6</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
-        <v>4.65</v>
+        <v>6.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.44</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>6.25</v>
+        <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>6.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="S12" t="n">
-        <v>3.22</v>
+        <v>4.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.49</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.15</v>
+        <v>6.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.11</v>
+        <v>3.8</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46048.58333333334</v>
+        <v>46048.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.22</v>
+        <v>2.08</v>
       </c>
       <c r="M14" t="n">
-        <v>6.3</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>8.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>2.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>4.15</v>
+        <v>7.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.3</v>
+        <v>3.1</v>
       </c>
       <c r="AA14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AH14" t="n">
-        <v>3.8</v>
+        <v>1.58</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46048.60416666666</v>
+        <v>46048.625</v>
       </c>
     </row>
     <row r="15">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="T15" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.02</v>
       </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
         <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.11</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
-        <v>2.77</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>8.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.54</v>
+        <v>1.73</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>1.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="V16" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z16" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH16" t="n">
         <v>3.1</v>
       </c>
-      <c r="AA16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AI16" s="3" t="n">
-        <v>46048.625</v>
+        <v>46048.66666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="V17" t="n">
-        <v>5.1</v>
+        <v>4.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.6</v>
+        <v>5.93</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.5</v>
+        <v>4.05</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="V18" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.05</v>
+        <v>4.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.81</v>
+        <v>1.49</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.01</v>
+        <v>1.72</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.5</v>
+        <v>3.77</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="U19" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="V19" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.72</v>
+        <v>3.01</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.77</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="T20" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="U20" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="V20" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.95</v>
+        <v>5.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC22" t="n">
         <v>3.7</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46048.66666666666</v>
+        <v>46048.6875</v>
       </c>
     </row>
     <row r="23">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.58</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="S23" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.75</v>
+        <v>4.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,34 +3277,34 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.84</v>
+        <v>5.8</v>
       </c>
       <c r="O24" t="n">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="P24" t="n">
         <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V24" t="n">
         <v>7.5</v>
@@ -3313,37 +3313,37 @@
         <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z24" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="AH24" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,76 +3396,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.17</v>
+        <v>2.63</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="U25" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="V25" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.65</v>
+        <v>4.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE25" t="n">
         <v>2.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46048.6875</v>
+        <v>46048.69791666666</v>
       </c>
     </row>
     <row r="26">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,19 +3634,19 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
         <v>3.4</v>
@@ -3655,55 +3655,55 @@
         <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="T27" t="n">
-        <v>3.64</v>
+        <v>3.24</v>
       </c>
       <c r="U27" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.85</v>
+        <v>4.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46048.69791666666</v>
+        <v>46048.70833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S28" t="n">
-        <v>2.57</v>
+        <v>2.2</v>
       </c>
       <c r="T28" t="n">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="V28" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
         <v>1.08</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.84</v>
+        <v>2.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.2</v>
+        <v>5.65</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG28" t="n">
         <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,76 +3991,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>7.75</v>
       </c>
       <c r="O30" t="n">
-        <v>2.7</v>
+        <v>1.92</v>
       </c>
       <c r="P30" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.25</v>
       </c>
-      <c r="V30" t="n">
-        <v>12</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AE30" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.73</v>
+        <v>2.97</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46048.70833333334</v>
+        <v>46048.71875</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,76 +4110,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46048.71875</v>
+        <v>46048.79166666666</v>
       </c>
     </row>
     <row r="32">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4298,125 +4298,6 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46048.79166666666</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46048</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Racing United</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Portmore United</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="3" t="n">
         <v>46048.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46048.15277777778</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O10" t="n">
-        <v>3.9</v>
+        <v>6.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.46</v>
+        <v>1.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AB10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6.25</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.3</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.5</v>
+        <v>10.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="S12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="V12" t="n">
-        <v>4.15</v>
+        <v>3.72</v>
       </c>
       <c r="W12" t="n">
         <v>1.2</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.6</v>
+        <v>6.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>3.72</v>
+        <v>4.15</v>
       </c>
       <c r="W13" t="n">
         <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.5</v>
+        <v>4.17</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>3.36</v>
       </c>
       <c r="T16" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.05</v>
+        <v>4.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.81</v>
+        <v>1.49</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="U17" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="V17" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.93</v>
+        <v>5.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="O18" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="U18" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.6</v>
+        <v>5.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.72</v>
+        <v>3.01</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.77</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="T19" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="U19" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.01</v>
+        <v>1.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>5.21</v>
       </c>
       <c r="N20" t="n">
-        <v>2.16</v>
+        <v>5.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V20" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.7</v>
+        <v>1.16</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>2.89</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2929,7 +2929,7 @@
         <v>4.65</v>
       </c>
       <c r="O21" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="P21" t="n">
         <v>2.53</v>
@@ -2941,16 +2941,16 @@
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="U21" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="V21" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="W21" t="n">
         <v>1.15</v>
@@ -2962,31 +2962,31 @@
         <v>1.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.4</v>
+        <v>5.54</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AB21" t="n">
         <v>2.66</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AD21" t="n">
         <v>1.72</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AG21" t="n">
         <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3405,13 +3405,13 @@
         <v>2.76</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="R25" t="n">
         <v>1.5</v>
@@ -3429,16 +3429,16 @@
         <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
         <v>1.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="AA25" t="n">
         <v>2.5</v>
@@ -3450,13 +3450,13 @@
         <v>4.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
         <v>2.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG25" t="n">
         <v>1.36</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>2.04</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="R27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U27" t="n">
         <v>1.5</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V27" t="n">
-        <v>8.5</v>
+        <v>5.6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.84</v>
+        <v>4.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.2</v>
+        <v>2.51</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="T28" t="n">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="U28" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
         <v>1.08</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.65</v>
+        <v>4.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
         <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.04</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
-        <v>3.58</v>
+        <v>2.7</v>
       </c>
       <c r="P29" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V29" t="n">
+        <v>12</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA29" t="n">
         <v>2.72</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.51</v>
+        <v>5.65</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.38</v>
+        <v>1.73</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI32"/>
+  <dimension ref="A1:AI33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.25</v>
+        <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>0.08</v>
       </c>
       <c r="O2" t="n">
         <v>2.63</v>
@@ -704,19 +704,19 @@
         <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AF2" t="n">
         <v>2.3</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1019,16 +1019,16 @@
         <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
         <v>4.8</v>
@@ -1064,13 +1064,13 @@
         <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC5" t="n">
         <v>2.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
         <v>1.7</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>5.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
         <v>1.37</v>
@@ -1412,10 +1412,10 @@
         <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA8" t="n">
         <v>1.91</v>
@@ -1424,10 +1424,10 @@
         <v>1.79</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
         <v>2.01</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,80 +1488,80 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>3.81</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>4.72</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.15</v>
+        <v>3.89</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE9" t="n">
         <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46048.51388888889</v>
+        <v>46048.5</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.6</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>4.65</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>1.44</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>6.25</v>
+        <v>2.55</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>3.22</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.15</v>
+        <v>2.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.6</v>
+        <v>4.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46048.58333333334</v>
+        <v>46048.51388888889</v>
       </c>
     </row>
     <row r="11">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>4.94</v>
       </c>
       <c r="P12" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.6</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5</v>
+        <v>3.22</v>
       </c>
       <c r="T12" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="U12" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="V12" t="n">
-        <v>3.72</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.2</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH12" t="n">
-        <v>4.5</v>
+        <v>1.11</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46048.60416666666</v>
+        <v>46048.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.5</v>
+        <v>10.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="V13" t="n">
-        <v>4.15</v>
+        <v>3.72</v>
       </c>
       <c r="W13" t="n">
         <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.8</v>
+        <v>5.88</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>6.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="P14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.98</v>
-      </c>
       <c r="U14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.33</v>
       </c>
-      <c r="V14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.68</v>
+        <v>2.83</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>1.96</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.58</v>
+        <v>3.04</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46048.625</v>
+        <v>46048.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="M15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.77</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.87</v>
-      </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
         <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.8</v>
+        <v>3.11</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>2.77</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>3.54</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.17</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>3.36</v>
+        <v>2.54</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>3.28</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.45</v>
+        <v>1.96</v>
       </c>
       <c r="AG16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.23</v>
       </c>
-      <c r="AH16" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AI16" s="3" t="n">
-        <v>46048.66666666666</v>
+        <v>46048.625</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB17" t="n">
         <v>2.3</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.96</v>
-      </c>
       <c r="AC17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.92</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.01</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>5.21</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V19" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.7</v>
+        <v>1.16</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>2.89</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="M20" t="n">
-        <v>5.21</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="T20" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="U20" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="V20" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.26</v>
+        <v>2.94</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.89</v>
+        <v>1.85</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>3.01</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>3.84</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>3.68</v>
       </c>
       <c r="T22" t="n">
-        <v>3.11</v>
+        <v>2.09</v>
       </c>
       <c r="U22" t="n">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.99</v>
+        <v>5.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.68</v>
+        <v>2.63</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="AG22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.33</v>
       </c>
-      <c r="AH22" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AI22" s="3" t="n">
-        <v>46048.6875</v>
+        <v>46048.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="U23" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.4</v>
+        <v>2.99</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.65</v>
+        <v>3.44</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.58</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.44</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC24" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,76 +3396,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.63</v>
+        <v>1.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.76</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.22</v>
+        <v>5.59</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="T25" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="U25" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.85</v>
+        <v>3.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46048.69791666666</v>
+        <v>46048.6875</v>
       </c>
     </row>
     <row r="26">
@@ -3530,7 +3530,7 @@
         <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
         <v>1.48</v>
@@ -3539,13 +3539,13 @@
         <v>2.45</v>
       </c>
       <c r="T26" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="U26" t="n">
         <v>1.3</v>
       </c>
       <c r="V26" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="W26" t="n">
         <v>1.02</v>
@@ -3557,7 +3557,7 @@
         <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="AA26" t="n">
         <v>2.18</v>
@@ -3572,13 +3572,13 @@
         <v>1.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
         <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
         <v>1.5</v>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,76 +3634,76 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O27" t="n">
         <v>3.45</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.58</v>
-      </c>
       <c r="P27" t="n">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.72</v>
+        <v>3.22</v>
       </c>
       <c r="R27" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.41</v>
+        <v>3.64</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="V27" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.51</v>
+        <v>4.85</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46048.70833333334</v>
+        <v>46048.69791666666</v>
       </c>
     </row>
     <row r="28">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>5.09</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="S28" t="n">
-        <v>2.57</v>
+        <v>2.26</v>
       </c>
       <c r="T28" t="n">
-        <v>3.24</v>
+        <v>4.05</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="V28" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="AA28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE28" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG28" t="n">
         <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="O29" t="n">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>2.72</v>
       </c>
       <c r="R29" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="T29" t="n">
-        <v>3.75</v>
+        <v>2.48</v>
       </c>
       <c r="U29" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>12</v>
+        <v>5.75</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.73</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,76 +3991,76 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.4</v>
       </c>
-      <c r="M30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="Z30" t="n">
         <v>2.9</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.72</v>
+        <v>4.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.97</v>
+        <v>1.56</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46048.71875</v>
+        <v>46048.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,76 +4110,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46048.79166666666</v>
+        <v>46048.71875</v>
       </c>
     </row>
     <row r="32">
@@ -4188,116 +4188,235 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Dunbeholden</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Harbour View</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="n">
+        <v>46048.79166666666</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Racing United</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Portmore United</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="3" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3" t="n">
         <v>46048.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI33"/>
+  <dimension ref="A1:AI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.06</v>
+        <v>2.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
         <v>2.63</v>
@@ -677,10 +677,10 @@
         <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
         <v>2.39</v>
@@ -689,7 +689,7 @@
         <v>1.51</v>
       </c>
       <c r="V2" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.09</v>
@@ -704,19 +704,19 @@
         <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AF2" t="n">
         <v>2.3</v>
@@ -1391,19 +1391,19 @@
         <v>5.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="T8" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="U8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
@@ -1412,10 +1412,10 @@
         <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AA8" t="n">
         <v>1.91</v>
@@ -1424,13 +1424,13 @@
         <v>1.79</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
         <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AF8" t="n">
         <v>1.75</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,80 +1488,80 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T9" t="n">
         <v>3.1</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.99</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.89</v>
+        <v>4.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.23</v>
+        <v>1.78</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46048.5</v>
+        <v>46048.51388888889</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.62</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="W10" t="n">
         <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.74</v>
+        <v>3.71</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.26</v>
+        <v>1.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46048.51388888889</v>
+        <v>46048.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>4.94</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="T11" t="n">
         <v>2.48</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="V11" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.92</v>
+        <v>2.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>4.65</v>
+        <v>6.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>4.94</v>
+        <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>7.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="S12" t="n">
-        <v>3.22</v>
+        <v>4.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.66</v>
       </c>
-      <c r="AB12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.11</v>
+        <v>3.04</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46048.58333333334</v>
+        <v>46048.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.33</v>
       </c>
-      <c r="M14" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AH14" t="n">
-        <v>3.04</v>
+        <v>1.23</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46048.60416666666</v>
+        <v>46048.625</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.33</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>2.9</v>
@@ -2227,37 +2227,37 @@
         <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
         <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.11</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
-        <v>2.77</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.54</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>4.17</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>2.54</v>
+        <v>3.36</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.28</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.96</v>
+        <v>2.45</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.23</v>
+        <v>1.92</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46048.625</v>
+        <v>46048.66666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>5.21</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.17</v>
+        <v>5.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.57</v>
       </c>
-      <c r="V17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AF17" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.92</v>
+        <v>2.89</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="T18" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
         <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
-        <v>5.21</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="O19" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="R19" t="n">
         <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="U19" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="V19" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>5.54</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.89</v>
+        <v>2.3</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.72</v>
+        <v>3.01</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="T20" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="U20" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="V20" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V21" t="n">
         <v>4.5</v>
       </c>
-      <c r="N21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.45</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.54</v>
+        <v>5.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.01</v>
+        <v>1.68</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.21</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.36</v>
+        <v>1.97</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>2.03</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46048.66666666666</v>
+        <v>46048.6875</v>
       </c>
     </row>
     <row r="23">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.5</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.09</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y23" t="n">
         <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.99</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.18</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.49</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,76 +3396,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.68</v>
+        <v>2.66</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.59</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="U25" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="V25" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.5</v>
+        <v>4.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AF25" t="n">
         <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.12</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46048.6875</v>
+        <v>46048.69791666666</v>
       </c>
     </row>
     <row r="26">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,76 +3634,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
         <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="T27" t="n">
-        <v>3.64</v>
+        <v>3.24</v>
       </c>
       <c r="U27" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.68</v>
+        <v>3.09</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.85</v>
+        <v>4.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46048.69791666666</v>
+        <v>46048.70833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.08</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>2.04</v>
       </c>
       <c r="O28" t="n">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="P28" t="n">
-        <v>1.97</v>
+        <v>2.21</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.09</v>
+        <v>2.72</v>
       </c>
       <c r="R28" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="S28" t="n">
-        <v>2.26</v>
+        <v>3.15</v>
       </c>
       <c r="T28" t="n">
-        <v>4.05</v>
+        <v>2.48</v>
       </c>
       <c r="U28" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>10</v>
+        <v>5.55</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="Z28" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF28" t="n">
         <v>2.3</v>
       </c>
-      <c r="AA28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.73</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O29" t="n">
         <v>2.7</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.58</v>
-      </c>
       <c r="P29" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.72</v>
+        <v>4.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="T29" t="n">
-        <v>2.48</v>
+        <v>4.05</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="V29" t="n">
-        <v>5.75</v>
+        <v>10.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.16</v>
+        <v>1.65</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.67</v>
+        <v>2.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.85</v>
+        <v>6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,76 +3991,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.19</v>
+        <v>4.5</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>7.75</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>2.57</v>
+        <v>2.69</v>
       </c>
       <c r="T30" t="n">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="U30" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V30" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH30" t="n">
         <v>2.9</v>
       </c>
-      <c r="AA30" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AI30" s="3" t="n">
-        <v>46048.70833333334</v>
+        <v>46048.71875</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,76 +4110,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46048.71875</v>
+        <v>46048.79166666666</v>
       </c>
     </row>
     <row r="32">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4298,125 +4298,6 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46048.79166666666</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46048</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Racing United</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Portmore United</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="3" t="n">
         <v>46048.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI32"/>
+  <dimension ref="A1:AI33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,16 +1019,16 @@
         <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
         <v>4.8</v>
@@ -1061,28 +1061,28 @@
         <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46048.375</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
         <v>2</v>
@@ -1391,49 +1391,49 @@
         <v>5.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="T8" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V8" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
         <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
         <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG8" t="n">
         <v>1.25</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,80 +1488,80 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>2.55</v>
+        <v>4.72</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="V9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.78</v>
+        <v>1.23</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46048.51388888889</v>
+        <v>46048.5</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="O10" t="n">
-        <v>3.95</v>
+        <v>2.55</v>
       </c>
       <c r="P10" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>5.07</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>2.47</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>6.4</v>
+        <v>8.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.71</v>
+        <v>2.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46048.58333333334</v>
+        <v>46048.51388888889</v>
       </c>
     </row>
     <row r="11">
@@ -1736,7 +1736,7 @@
         <v>4.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="O11" t="n">
         <v>4.94</v>
@@ -1745,25 +1745,25 @@
         <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="T11" t="n">
         <v>2.48</v>
       </c>
       <c r="U11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V11" t="n">
         <v>5.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
@@ -1772,19 +1772,19 @@
         <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.15</v>
+        <v>4.49</v>
       </c>
       <c r="AA11" t="n">
         <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
         <v>1.84</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.33</v>
       </c>
-      <c r="M12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="AE12" t="n">
         <v>1.67</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="AF12" t="n">
         <v>2.05</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.04</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46048.60416666666</v>
+        <v>46048.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="P13" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.6</v>
+        <v>7.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="U13" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>3.72</v>
+        <v>4.15</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>5.63</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.99</v>
+        <v>1.66</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.88</v>
+        <v>3.54</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.54</v>
+        <v>1.52</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>8.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="V14" t="n">
-        <v>6.1</v>
+        <v>3.72</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.1</v>
+        <v>6.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>1.28</v>
       </c>
       <c r="AB14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.77</v>
       </c>
-      <c r="AC14" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.23</v>
+        <v>5.88</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46048.625</v>
+        <v>46048.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.14</v>
+        <v>3.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
         <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="T15" t="n">
         <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>2.91</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.17</v>
+        <v>3.82</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>3.36</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46048.66666666666</v>
+        <v>46048.625</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.4</v>
+        <v>2.73</v>
       </c>
       <c r="M17" t="n">
-        <v>5.21</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z17" t="n">
         <v>5.5</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6</v>
-      </c>
       <c r="AA17" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.89</v>
+        <v>1.33</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>2.3</v>
@@ -2593,10 +2593,10 @@
         <v>1.77</v>
       </c>
       <c r="V18" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
@@ -2608,16 +2608,16 @@
         <v>5.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="AC18" t="n">
         <v>1.92</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE18" t="n">
         <v>1.35</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.57</v>
       </c>
-      <c r="M19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.69</v>
-      </c>
       <c r="V19" t="n">
-        <v>4.45</v>
+        <v>5.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.54</v>
+        <v>4.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.66</v>
+        <v>2.35</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AF19" t="n">
         <v>2.45</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.01</v>
+        <v>1.38</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>6.42</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V20" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH20" t="n">
         <v>2.8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.63</v>
+        <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>2.03</v>
       </c>
       <c r="P21" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S21" t="n">
-        <v>3.68</v>
+        <v>3.92</v>
       </c>
       <c r="T21" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V21" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="W21" t="n">
         <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
         <v>5.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.53</v>
+        <v>2.29</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.68</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.36</v>
       </c>
-      <c r="V22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.73</v>
+        <v>2.86</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46048.6875</v>
+        <v>46048.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC23" t="n">
         <v>3.5</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="AD23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="P24" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
         <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y24" t="n">
         <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE24" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,76 +3396,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.66</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z25" t="n">
         <v>3.1</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V25" t="n">
-        <v>9</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AA25" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.85</v>
+        <v>3.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46048.69791666666</v>
+        <v>46048.6875</v>
       </c>
     </row>
     <row r="26">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="N26" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
         <v>3.27</v>
@@ -3536,16 +3536,16 @@
         <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="T26" t="n">
         <v>3.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W26" t="n">
         <v>1.02</v>
@@ -3560,10 +3560,10 @@
         <v>2.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC26" t="n">
         <v>4.2</v>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,76 +3634,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
         <v>3.4</v>
       </c>
       <c r="R27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V27" t="n">
+        <v>9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.5</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V27" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AC27" t="n">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46048.70833333334</v>
+        <v>46048.69791666666</v>
       </c>
     </row>
     <row r="28">
@@ -3753,22 +3753,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="O28" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="R28" t="n">
         <v>1.31</v>
@@ -3780,7 +3780,7 @@
         <v>2.48</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="V28" t="n">
         <v>5.55</v>
@@ -3798,28 +3798,28 @@
         <v>4.15</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.85</v>
+        <v>2.51</v>
       </c>
       <c r="AD28" t="n">
         <v>1.42</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.63</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="N29" t="n">
         <v>3.65</v>
@@ -3884,16 +3884,16 @@
         <v>2.7</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="S29" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="T29" t="n">
         <v>4.05</v>
@@ -3902,40 +3902,40 @@
         <v>1.22</v>
       </c>
       <c r="V29" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC29" t="n">
-        <v>6</v>
+        <v>5.65</v>
       </c>
       <c r="AD29" t="n">
         <v>1.13</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AF29" t="n">
         <v>1.6</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
         <v>1.73</v>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,76 +3991,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="M30" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>7.75</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.85</v>
+        <v>2.87</v>
       </c>
       <c r="P30" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="T30" t="n">
-        <v>2.94</v>
+        <v>3.24</v>
       </c>
       <c r="U30" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V30" t="n">
-        <v>6.95</v>
+        <v>8.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.72</v>
+        <v>4.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.9</v>
+        <v>1.56</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46048.71875</v>
+        <v>46048.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,76 +4110,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46048.79166666666</v>
+        <v>46048.71875</v>
       </c>
     </row>
     <row r="32">
@@ -4188,116 +4188,235 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Dunbeholden</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Harbour View</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="n">
+        <v>46048.79166666666</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Racing United</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Portmore United</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="3" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3" t="n">
         <v>46048.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.13</v>
+        <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>0.08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="P2" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
@@ -689,43 +689,43 @@
         <v>1.51</v>
       </c>
       <c r="V2" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W2" t="n">
         <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
         <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AC2" t="n">
         <v>2.51</v>
       </c>
       <c r="AD2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.53</v>
       </c>
       <c r="AF2" t="n">
         <v>2.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46048.15277777778</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P8" t="n">
         <v>2</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.32</v>
-      </c>
       <c r="Q8" t="n">
-        <v>5.22</v>
+        <v>2.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="U8" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.4</v>
+        <v>1.23</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46048.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>1.51</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="O9" t="n">
-        <v>4.72</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.64</v>
+        <v>5.22</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>2.54</v>
+        <v>2.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="U9" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA9" t="n">
         <v>1.96</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.23</v>
+        <v>2.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.94</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.49</v>
+        <v>3.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>4.94</v>
       </c>
       <c r="P12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB12" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
         <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>3.01</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>2.91</v>
       </c>
       <c r="P15" t="n">
         <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
         <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
         <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.01</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.91</v>
+        <v>3.54</v>
       </c>
       <c r="P16" t="n">
         <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="T16" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
         <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.73</v>
+        <v>1.56</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.1</v>
       </c>
-      <c r="O17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.09</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="V17" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="W17" t="n">
         <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA17" t="n">
         <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AC17" t="n">
         <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.7</v>
+        <v>1.16</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.33</v>
+        <v>2.33</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="M18" t="n">
         <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
         <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>3.77</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
@@ -2587,16 +2587,16 @@
         <v>4.05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V18" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
@@ -2608,22 +2608,22 @@
         <v>5.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AG18" t="n">
         <v>1.2</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,40 +2682,40 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.8</v>
+        <v>3.01</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.33</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.23</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="V19" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
@@ -2724,31 +2724,31 @@
         <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.92</v>
+        <v>1.35</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2801,22 +2801,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="N20" t="n">
         <v>6.42</v>
       </c>
       <c r="O20" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="P20" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
@@ -2828,10 +2828,10 @@
         <v>2.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V20" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="W20" t="n">
         <v>1.16</v>
@@ -2840,22 +2840,22 @@
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE20" t="n">
         <v>1.57</v>
@@ -2864,10 +2864,10 @@
         <v>2.24</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="M21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S21" t="n">
         <v>4</v>
       </c>
-      <c r="N21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="T21" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V21" t="n">
         <v>4.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.45</v>
       </c>
       <c r="W21" t="n">
         <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.29</v>
+        <v>1.53</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8</v>
+        <v>4.23</v>
       </c>
       <c r="R22" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="V22" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.86</v>
+        <v>2.41</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.5</v>
       </c>
-      <c r="N23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.44</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AC23" t="n">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="O24" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC24" t="n">
         <v>3.5</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="AD24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3518,19 +3518,19 @@
         <v>2.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="O26" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
         <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
         <v>1.48</v>
@@ -3557,10 +3557,10 @@
         <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AB26" t="n">
         <v>1.59</v>
@@ -3572,13 +3572,13 @@
         <v>1.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
         <v>1.5</v>
@@ -3637,7 +3637,7 @@
         <v>2.66</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
         <v>2.71</v>
@@ -3646,40 +3646,40 @@
         <v>3.45</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q27" t="n">
         <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
         <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
         <v>1.26</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="W27" t="n">
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y27" t="n">
         <v>1.46</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AB27" t="n">
         <v>1.5</v>
@@ -3691,13 +3691,13 @@
         <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AF27" t="n">
         <v>1.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH27" t="n">
         <v>1.44</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O28" t="n">
         <v>2.7</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3.5</v>
-      </c>
       <c r="P28" t="n">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.71</v>
+        <v>4.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="S28" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
-        <v>2.48</v>
+        <v>4.05</v>
       </c>
       <c r="U28" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="V28" t="n">
-        <v>5.55</v>
+        <v>12</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.16</v>
+        <v>1.61</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.15</v>
+        <v>2.42</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.67</v>
+        <v>2.72</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.51</v>
+        <v>5.65</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.53</v>
+        <v>2.28</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.37</v>
+        <v>1.6</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M29" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="O29" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V29" t="n">
+        <v>7</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T29" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V29" t="n">
-        <v>12</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AF29" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>2.19</v>
       </c>
       <c r="O30" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>2.57</v>
+        <v>3.15</v>
       </c>
       <c r="T30" t="n">
-        <v>3.24</v>
+        <v>2.41</v>
       </c>
       <c r="U30" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
-        <v>8.5</v>
+        <v>5.55</v>
       </c>
       <c r="W30" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46048.70833333334</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.1</v>
+        <v>1.51</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.64</v>
+        <v>5.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="T8" t="n">
-        <v>3.22</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.23</v>
+        <v>2.4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46048.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.32</v>
-      </c>
       <c r="Q9" t="n">
-        <v>5.22</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="U9" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.4</v>
+        <v>1.23</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.02</v>
+        <v>8.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="V13" t="n">
-        <v>4.15</v>
+        <v>3.72</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.63</v>
+        <v>6.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.54</v>
+        <v>5.88</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="P14" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.5</v>
+        <v>7.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>3.72</v>
+        <v>4.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.75</v>
+        <v>5.63</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.99</v>
+        <v>1.66</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.88</v>
+        <v>3.54</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="M15" t="n">
         <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.01</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.91</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
         <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="T15" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
         <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="M16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.2</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.1</v>
-      </c>
       <c r="O16" t="n">
-        <v>3.54</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
         <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.54</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>6.42</v>
       </c>
       <c r="O17" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.6</v>
+        <v>5.55</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="V17" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.33</v>
+        <v>2.83</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="P18" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.77</v>
+        <v>4.6</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>4.05</v>
+        <v>3.94</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="V18" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.01</v>
+        <v>1.83</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.13</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="V19" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z20" t="n">
         <v>4.6</v>
       </c>
-      <c r="N20" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.83</v>
+        <v>1.93</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.28</v>
+        <v>3.01</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
         <v>2.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="U21" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V21" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.38</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="M22" t="n">
         <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="O22" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.23</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="U22" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="V22" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.41</v>
+        <v>2.9</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S23" t="n">
         <v>2.8</v>
       </c>
-      <c r="N23" t="n">
+      <c r="T23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z23" t="n">
         <v>3.1</v>
       </c>
-      <c r="O23" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AA23" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.65</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T24" t="n">
         <v>3.5</v>
       </c>
-      <c r="N24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="U24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.44</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AC24" t="n">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="T25" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46048.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
         <v>3.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
         <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="AD26" t="n">
         <v>1.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="O27" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="T27" t="n">
         <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V27" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
         <v>1.08</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.85</v>
+        <v>4.2</v>
       </c>
       <c r="AD27" t="n">
         <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.1</v>
+        <v>2.68</v>
       </c>
       <c r="M28" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>2.19</v>
       </c>
       <c r="O28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2.7</v>
       </c>
-      <c r="P28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4.6</v>
-      </c>
       <c r="R28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.53</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T28" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V28" t="n">
-        <v>12</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.68</v>
+        <v>2.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="N30" t="n">
-        <v>2.19</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="S30" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="T30" t="n">
-        <v>2.41</v>
+        <v>4.05</v>
       </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="V30" t="n">
-        <v>5.55</v>
+        <v>12</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.21</v>
+        <v>1.61</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.65</v>
+        <v>2.72</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.85</v>
+        <v>5.65</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.53</v>
+        <v>2.28</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46048.70833333334</v>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.06</v>
+        <v>2.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06</v>
+        <v>3.59</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08</v>
+        <v>2.88</v>
       </c>
       <c r="O2" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
@@ -683,19 +683,19 @@
         <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
         <v>5.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
         <v>1.17</v>
@@ -704,19 +704,19 @@
         <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF2" t="n">
         <v>2.3</v>
@@ -725,7 +725,7 @@
         <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46048.15277777778</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M3" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="N3" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1144,34 +1144,34 @@
         <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
         <v>1.63</v>
@@ -1180,28 +1180,28 @@
         <v>2.13</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46048.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P8" t="n">
         <v>2</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.32</v>
-      </c>
       <c r="Q8" t="n">
-        <v>5.22</v>
+        <v>2.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="U8" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.4</v>
+        <v>1.23</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46048.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="O9" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.64</v>
+        <v>5.75</v>
       </c>
       <c r="R9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.36</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.83</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.23</v>
+        <v>2.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.5</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.07</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
         <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V10" t="n">
         <v>8.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.51388888889</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>4.94</v>
       </c>
       <c r="P11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB11" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AC11" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.94</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.49</v>
+        <v>3.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1977,16 +1977,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.5</v>
+        <v>10.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S13" t="n">
         <v>4.5</v>
@@ -2007,34 +2007,34 @@
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="n">
         <v>1.99</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.88</v>
+        <v>5.25</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2087,22 +2087,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="M14" t="n">
-        <v>6.3</v>
+        <v>6.05</v>
       </c>
       <c r="N14" t="n">
-        <v>7.8</v>
+        <v>9.5</v>
       </c>
       <c r="O14" t="n">
         <v>1.65</v>
       </c>
       <c r="P14" t="n">
-        <v>2.92</v>
+        <v>3.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.02</v>
+        <v>6.8</v>
       </c>
       <c r="R14" t="n">
         <v>1.14</v>
@@ -2111,10 +2111,10 @@
         <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="U14" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V14" t="n">
         <v>4.15</v>
@@ -2126,34 +2126,34 @@
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.63</v>
+        <v>7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
         <v>3.54</v>
@@ -2236,7 +2236,7 @@
         <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
@@ -2245,13 +2245,13 @@
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
         <v>1.77</v>
@@ -2260,10 +2260,10 @@
         <v>3.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
         <v>1.95</v>
@@ -2385,7 +2385,7 @@
         <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
         <v>1.34</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>2.28</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>6.42</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>1.79</v>
+        <v>2.65</v>
       </c>
       <c r="P17" t="n">
-        <v>2.68</v>
+        <v>2.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.55</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
       </c>
       <c r="T17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.05</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="AD17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF17" t="n">
-        <v>2.24</v>
+        <v>2.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.83</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.56</v>
+        <v>3.01</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>4.6</v>
-      </c>
       <c r="R18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.18</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.14</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z18" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="AC18" t="n">
         <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.33</v>
+        <v>1.35</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="P19" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.77</v>
+        <v>4.6</v>
       </c>
       <c r="R19" t="n">
         <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>4.05</v>
+        <v>3.94</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="V19" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>6.42</v>
       </c>
       <c r="O20" t="n">
-        <v>2.33</v>
+        <v>1.79</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.23</v>
+        <v>5.55</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.57</v>
       </c>
-      <c r="V20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="AF20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.11</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.93</v>
+        <v>2.83</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.01</v>
+        <v>1.83</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="O21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.13</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="V21" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
         <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="P22" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>4.23</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="V22" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.9</v>
+        <v>2.41</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="M23" t="n">
-        <v>3.49</v>
+        <v>2.77</v>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.5</v>
+        <v>4.08</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="T23" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z24" t="n">
         <v>3.1</v>
       </c>
-      <c r="O24" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AA24" t="n">
-        <v>2.49</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3396,19 +3396,19 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="N25" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O25" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
         <v>5</v>
@@ -3420,13 +3420,13 @@
         <v>2.47</v>
       </c>
       <c r="T25" t="n">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="W25" t="n">
         <v>1.03</v>
@@ -3435,34 +3435,34 @@
         <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AF25" t="n">
         <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46048.6875</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="O26" t="n">
         <v>3.45</v>
@@ -3560,10 +3560,10 @@
         <v>2.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>4.85</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N27" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -3655,13 +3655,13 @@
         <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="U27" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V27" t="n">
         <v>8.199999999999999</v>
@@ -3670,19 +3670,19 @@
         <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC27" t="n">
         <v>4.2</v>
@@ -3691,10 +3691,10 @@
         <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
         <v>1.36</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.68</v>
+        <v>0.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>0.29</v>
       </c>
       <c r="N28" t="n">
-        <v>2.19</v>
+        <v>0.39</v>
       </c>
       <c r="O28" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA28" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC28" t="n">
         <v>4.2</v>
       </c>
-      <c r="AA28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.85</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T29" t="n">
         <v>2.4</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
         <v>1.5</v>
       </c>
-      <c r="S29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V29" t="n">
-        <v>7</v>
+        <v>5.55</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AG29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.37</v>
+        <v>0.53</v>
       </c>
       <c r="M31" t="n">
-        <v>4.58</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>9.5</v>
+        <v>0.05</v>
       </c>
       <c r="O31" t="n">
         <v>2</v>
@@ -4134,7 +4134,7 @@
         <v>2.8</v>
       </c>
       <c r="T31" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="U31" t="n">
         <v>1.4</v>
@@ -4149,22 +4149,22 @@
         <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
         <v>2.46</v>
@@ -4176,7 +4176,7 @@
         <v>1.02</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46048.71875</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
         <v>3.18</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI33"/>
+  <dimension ref="A1:AI31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,7 +677,7 @@
         <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
         <v>3.15</v>
@@ -695,7 +695,7 @@
         <v>1.12</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
         <v>1.17</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1019,13 +1019,13 @@
         <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="P5" t="n">
         <v>2.3</v>
@@ -1034,19 +1034,19 @@
         <v>4.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="T5" t="n">
         <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="W5" t="n">
         <v>1.06</v>
@@ -1064,22 +1064,22 @@
         <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF5" t="n">
         <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH5" t="n">
         <v>2.2</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46048.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46048.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.87</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.23</v>
+        <v>2.43</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46048.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>6.2</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q9" t="n">
-        <v>5.75</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
         <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.5</v>
@@ -1736,43 +1736,43 @@
         <v>4.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="O11" t="n">
-        <v>4.94</v>
+        <v>5.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="T11" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="V11" t="n">
         <v>5.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="AA11" t="n">
         <v>1.66</v>
@@ -1781,22 +1781,22 @@
         <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
         <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1858,25 +1858,25 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>4.47</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R12" t="n">
         <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
         <v>6.4</v>
@@ -1888,13 +1888,13 @@
         <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
         <v>1.91</v>
@@ -1909,10 +1909,10 @@
         <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="n">
         <v>1.25</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="P13" t="n">
-        <v>2.8</v>
+        <v>3.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.6</v>
+        <v>6.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="U13" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="V13" t="n">
-        <v>3.72</v>
+        <v>4.15</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.8</v>
+        <v>10.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.99</v>
       </c>
-      <c r="U14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AF14" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,43 +2206,43 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.11</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>2.92</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
         <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.54</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
         <v>1.28</v>
@@ -2251,28 +2251,28 @@
         <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.625</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,43 +2325,43 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.08</v>
+        <v>3.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>2.11</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>3.54</v>
       </c>
       <c r="P16" t="n">
         <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>2.54</v>
       </c>
       <c r="T16" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
         <v>1.28</v>
@@ -2370,28 +2370,28 @@
         <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD16" t="n">
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.34</v>
+        <v>1.73</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="P17" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>4.17</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="V17" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,40 +2563,40 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.01</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="P18" t="n">
         <v>2.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="U18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
@@ -2605,31 +2605,31 @@
         <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
         <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="O19" t="n">
         <v>2.08</v>
@@ -2697,13 +2697,13 @@
         <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="T19" t="n">
         <v>2.1</v>
@@ -2715,34 +2715,34 @@
         <v>4.33</v>
       </c>
       <c r="W19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.14</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z19" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA19" t="n">
         <v>1.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="AC19" t="n">
         <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG19" t="n">
         <v>1.16</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="M20" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>6.42</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.55</v>
+        <v>3.77</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="T20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="V20" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.24</v>
+        <v>2.94</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.83</v>
+        <v>1.85</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>5.23</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="P21" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.77</v>
+        <v>5.76</v>
       </c>
       <c r="R21" t="n">
         <v>1.18</v>
@@ -2944,49 +2944,49 @@
         <v>4.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="V21" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="n">
         <v>1.36</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>3.01</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>2.03</v>
       </c>
       <c r="O22" t="n">
-        <v>2.33</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.23</v>
+        <v>2.47</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="T22" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="V22" t="n">
-        <v>5.1</v>
+        <v>4.55</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.35</v>
+        <v>2.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.32</v>
+        <v>1.65</v>
       </c>
       <c r="M23" t="n">
-        <v>2.77</v>
+        <v>3.38</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.08</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.22</v>
       </c>
-      <c r="V23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH23" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="N24" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE24" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="M25" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>5.1</v>
+        <v>3.84</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
         <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46048.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="U26" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V26" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.85</v>
+        <v>4.2</v>
       </c>
       <c r="AD26" t="n">
         <v>1.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V27" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="AD27" t="n">
         <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="M28" t="n">
-        <v>0.29</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.39</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="S28" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="T28" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="V28" t="n">
-        <v>7.5</v>
+        <v>12</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AF28" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG28" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.45</v>
+        <v>0.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>0.29</v>
       </c>
       <c r="N29" t="n">
-        <v>2.04</v>
+        <v>0.39</v>
       </c>
       <c r="O29" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V29" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA29" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V29" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC29" t="n">
         <v>4.2</v>
       </c>
-      <c r="AA29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.85</v>
-      </c>
       <c r="AD29" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB30" t="n">
         <v>2.1</v>
       </c>
-      <c r="M30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T30" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V30" t="n">
-        <v>12</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AB30" t="n">
+      <c r="AC30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.44</v>
       </c>
-      <c r="AC30" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AE30" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46048.70833333334</v>
@@ -4131,16 +4131,16 @@
         <v>1.41</v>
       </c>
       <c r="S31" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="T31" t="n">
-        <v>3.13</v>
+        <v>2.94</v>
       </c>
       <c r="U31" t="n">
         <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.04</v>
@@ -4149,7 +4149,7 @@
         <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
         <v>3.1</v>
@@ -4180,244 +4180,6 @@
       </c>
       <c r="AI31" s="3" t="n">
         <v>46048.71875</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46048</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Dunbeholden</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Harbour View</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="3" t="n">
-        <v>46048.79166666666</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46048</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Racing United</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Portmore United</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="3" t="n">
-        <v>46048.89583333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI31"/>
+  <dimension ref="A1:AI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="M2" t="n">
-        <v>3.59</v>
+        <v>3.64</v>
       </c>
       <c r="N2" t="n">
         <v>2.88</v>
@@ -677,7 +677,7 @@
         <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
         <v>3.15</v>
@@ -686,25 +686,25 @@
         <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V2" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="W2" t="n">
         <v>1.12</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>4.43</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
         <v>2.21</v>
@@ -713,19 +713,19 @@
         <v>2.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46048.15277777778</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.85</v>
       </c>
       <c r="O5" t="n">
         <v>1.93</v>
@@ -1043,10 +1043,10 @@
         <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>6.05</v>
+        <v>5.5</v>
       </c>
       <c r="W5" t="n">
         <v>1.06</v>
@@ -1055,16 +1055,16 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AC5" t="n">
         <v>2.66</v>
@@ -1079,7 +1079,7 @@
         <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
         <v>2.2</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P8" t="n">
         <v>2</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q8" t="n">
-        <v>5.75</v>
+        <v>2.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.84</v>
+        <v>3.22</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.43</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46048.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="O9" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>2.43</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.5</v>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>4.72</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE10" t="n">
         <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46048.51388888889</v>
+        <v>46048.5</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>5.75</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>3.22</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>5.2</v>
+        <v>8.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46048.58333333334</v>
+        <v>46048.51388888889</v>
       </c>
     </row>
     <row r="12">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O12" t="n">
         <v>4.47</v>
@@ -1873,13 +1873,13 @@
         <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.05</v>
@@ -1900,7 +1900,7 @@
         <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD12" t="n">
         <v>1.33</v>
@@ -1912,7 +1912,7 @@
         <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
         <v>1.25</v>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>6.05</v>
+        <v>4.8</v>
       </c>
       <c r="N13" t="n">
-        <v>9.5</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.65</v>
+        <v>5.75</v>
       </c>
       <c r="P13" t="n">
-        <v>3.01</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.8</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>3.22</v>
       </c>
       <c r="T13" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="V13" t="n">
-        <v>4.15</v>
+        <v>5.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.11</v>
       </c>
-      <c r="AH13" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AI13" s="3" t="n">
-        <v>46048.60416666666</v>
+        <v>46048.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>1.22</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>6.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.92</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="P15" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>3.8</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46048.625</v>
+        <v>46048.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="N16" t="n">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="O16" t="n">
         <v>3.54</v>
@@ -2370,10 +2370,10 @@
         <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
         <v>3.28</v>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="O17" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.17</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.25</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="AE17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.57</v>
       </c>
-      <c r="V17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AI17" s="3" t="n">
-        <v>46048.66666666666</v>
+        <v>46048.625</v>
       </c>
     </row>
     <row r="18">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>4.65</v>
       </c>
       <c r="O18" t="n">
-        <v>2.65</v>
+        <v>2.08</v>
       </c>
       <c r="P18" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>4.55</v>
       </c>
       <c r="R18" t="n">
         <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="T18" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
         <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>5.23</v>
       </c>
       <c r="N19" t="n">
-        <v>4.65</v>
+        <v>5.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.55</v>
+        <v>5.76</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>3.92</v>
+        <v>4.05</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="V19" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
         <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>2.55</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="P20" t="n">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.77</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="U20" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="V20" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>3.01</v>
       </c>
       <c r="M21" t="n">
-        <v>5.23</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z21" t="n">
         <v>5.5</v>
       </c>
-      <c r="O21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6</v>
-      </c>
       <c r="AA21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AF21" t="n">
         <v>2.8</v>
       </c>
-      <c r="AC21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.24</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.01</v>
+        <v>1.87</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>2.03</v>
+        <v>3.55</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.47</v>
+        <v>3.77</v>
       </c>
       <c r="R22" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="V22" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,76 +3158,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>4.17</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>3.36</v>
       </c>
       <c r="T23" t="n">
-        <v>3.04</v>
+        <v>2.16</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="V23" t="n">
-        <v>7.3</v>
+        <v>4.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46048.6875</v>
+        <v>46048.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>3.84</v>
       </c>
       <c r="O24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.9</v>
       </c>
-      <c r="P24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N25" t="n">
-        <v>3.84</v>
+        <v>5.1</v>
       </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="T25" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="W25" t="n">
         <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA25" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH25" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46048.6875</v>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,76 +3515,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.5</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.31</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="V26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46048.69791666666</v>
+        <v>46048.6875</v>
       </c>
     </row>
     <row r="27">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,76 +3753,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="O28" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V28" t="n">
-        <v>12</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46048.70833333334</v>
+        <v>46048.69791666666</v>
       </c>
     </row>
     <row r="29">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.3</v>
+        <v>2.33</v>
       </c>
       <c r="M29" t="n">
-        <v>0.29</v>
+        <v>3.36</v>
       </c>
       <c r="N29" t="n">
-        <v>0.39</v>
+        <v>3.48</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="P30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S30" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.15</v>
-      </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="V30" t="n">
-        <v>5.55</v>
+        <v>12</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>1.61</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.66</v>
+        <v>2.89</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.85</v>
+        <v>5.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46048.70833333334</v>
@@ -4069,116 +4069,235 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI31" s="3" t="n">
+        <v>46048.70833333334</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Portugal Liga NOS</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Gil Vicente</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>7</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AI31" s="3" t="n">
+      <c r="L32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M32" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="N32" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="n">
         <v>46048.71875</v>
       </c>
     </row>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="M3" t="n">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="N3" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -900,70 +900,70 @@
         <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46048.35416666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46048.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46048.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="O8" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>2.43</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46048.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>6.2</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q9" t="n">
-        <v>5.75</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.84</v>
+        <v>3.22</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.43</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.5</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
         <v>3.3</v>
@@ -1751,19 +1751,19 @@
         <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="T11" t="n">
         <v>3.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1.06</v>
@@ -1781,7 +1781,7 @@
         <v>1.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="AD11" t="n">
         <v>1.2</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="O12" t="n">
-        <v>4.47</v>
+        <v>6.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="M13" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.4</v>
       </c>
-      <c r="O13" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="V13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.3</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.58333333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="P14" t="n">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.6</v>
+        <v>6.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="U14" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="V14" t="n">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="W14" t="n">
         <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="M15" t="n">
-        <v>6.05</v>
+        <v>8</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>14.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="P15" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.8</v>
+        <v>10.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.99</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.8</v>
+        <v>5.94</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,40 +2325,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.11</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>2.98</v>
       </c>
       <c r="O16" t="n">
-        <v>3.54</v>
+        <v>2.69</v>
       </c>
       <c r="P16" t="n">
         <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="U16" t="n">
         <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
@@ -2370,28 +2370,28 @@
         <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AD16" t="n">
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,43 +2444,43 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>3.11</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="N17" t="n">
-        <v>2.92</v>
+        <v>2.29</v>
       </c>
       <c r="O17" t="n">
-        <v>2.8</v>
+        <v>3.54</v>
       </c>
       <c r="P17" t="n">
         <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>2.54</v>
       </c>
       <c r="T17" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
         <v>1.28</v>
@@ -2489,28 +2489,28 @@
         <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD17" t="n">
         <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.625</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="M19" t="n">
-        <v>5.23</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.76</v>
+        <v>3.77</v>
       </c>
       <c r="R19" t="n">
         <v>1.18</v>
@@ -2706,49 +2706,49 @@
         <v>4.05</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="V19" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.24</v>
+        <v>2.94</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>3.01</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="O20" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
         <v>2.35</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="T20" t="n">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="U20" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V20" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE20" t="n">
         <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.01</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>5.23</v>
       </c>
       <c r="N21" t="n">
-        <v>2.03</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>1.79</v>
       </c>
       <c r="P21" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.47</v>
+        <v>5.76</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="T21" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V21" t="n">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH21" t="n">
         <v>2.8</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P22" t="n">
         <v>2.3</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.69</v>
-      </c>
       <c r="Q22" t="n">
-        <v>3.77</v>
+        <v>4.17</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>4.05</v>
+        <v>3.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="U22" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="V22" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.95</v>
+        <v>4.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,40 +3158,40 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="O23" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.17</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S23" t="n">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="U23" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="V23" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X23" t="n">
         <v>1.02</v>
@@ -3200,31 +3200,31 @@
         <v>1.14</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.6</v>
+        <v>5.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.84</v>
+        <v>4.36</v>
       </c>
       <c r="O24" t="n">
         <v>2.5</v>
@@ -3301,13 +3301,13 @@
         <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.03</v>
@@ -3322,10 +3322,10 @@
         <v>3.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>3.7</v>
@@ -3396,19 +3396,19 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M25" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
       <c r="O25" t="n">
         <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
         <v>5</v>
@@ -3420,7 +3420,7 @@
         <v>2.47</v>
       </c>
       <c r="T25" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="U25" t="n">
         <v>1.31</v>
@@ -3441,13 +3441,13 @@
         <v>2.88</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD25" t="n">
         <v>1.22</v>
@@ -3459,7 +3459,7 @@
         <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
         <v>2.05</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="O26" t="n">
         <v>2.9</v>
@@ -3530,13 +3530,13 @@
         <v>1.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.08</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
         <v>1.58</v>
       </c>
       <c r="S26" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="T26" t="n">
         <v>3.5</v>
@@ -3551,37 +3551,37 @@
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y26" t="n">
         <v>1.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC26" t="n">
         <v>3.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46048.6875</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="O27" t="n">
         <v>3.45</v>
@@ -3655,13 +3655,13 @@
         <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="T27" t="n">
         <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="V27" t="n">
         <v>10.5</v>
@@ -3670,19 +3670,19 @@
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y27" t="n">
         <v>1.46</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
         <v>4.85</v>
@@ -3694,7 +3694,7 @@
         <v>2.05</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
         <v>1.38</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.33</v>
+        <v>2.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>3.48</v>
+        <v>2.25</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="O30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.89</v>
+        <v>2.15</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46048.70833333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.04</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.7</v>
+        <v>4.95</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="S31" t="n">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="V31" t="n">
-        <v>5.55</v>
+        <v>10.5</v>
       </c>
       <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.08</v>
       </c>
-      <c r="X31" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.2</v>
+        <v>1.61</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.2</v>
+        <v>2.43</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.75</v>
+        <v>2.88</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>1.39</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.85</v>
+        <v>5.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46048.70833333334</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="M3" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
         <v>3.25</v>
@@ -1019,13 +1019,13 @@
         <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.85</v>
+        <v>4.49</v>
       </c>
       <c r="O5" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="P5" t="n">
         <v>2.3</v>
@@ -1037,16 +1037,16 @@
         <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
         <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="W5" t="n">
         <v>1.06</v>
@@ -1055,7 +1055,7 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
         <v>3.98</v>
@@ -1064,7 +1064,7 @@
         <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
         <v>2.66</v>
@@ -1079,7 +1079,7 @@
         <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AH5" t="n">
         <v>2.2</v>
@@ -1171,7 +1171,7 @@
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y6" t="n">
         <v>1.63</v>
@@ -1189,7 +1189,7 @@
         <v>6.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE6" t="n">
         <v>2.34</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>3.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.75</v>
+        <v>4.72</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.73</v>
+        <v>2.54</v>
       </c>
       <c r="T8" t="n">
-        <v>2.84</v>
+        <v>2.99</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>3.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.43</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46048.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.72</v>
+        <v>5.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.54</v>
+        <v>2.96</v>
       </c>
       <c r="T10" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.88</v>
+        <v>3.41</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.73</v>
+        <v>2.43</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.5</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
         <v>3.3</v>
@@ -1751,7 +1751,7 @@
         <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="T11" t="n">
         <v>3.1</v>
@@ -1760,13 +1760,13 @@
         <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
         <v>1.36</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="O12" t="n">
-        <v>6.45</v>
+        <v>4.33</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="R12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.3</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.7</v>
+        <v>7.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="N13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.91</v>
       </c>
-      <c r="O13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.58333333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="M14" t="n">
-        <v>6.05</v>
+        <v>8</v>
       </c>
       <c r="N14" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>3.07</v>
+        <v>3.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="S14" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="V14" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="W14" t="n">
         <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.8</v>
+        <v>5.94</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="M15" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="N15" t="n">
-        <v>14.2</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="P15" t="n">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>10.6</v>
+        <v>6.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="U15" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="V15" t="n">
-        <v>3.72</v>
+        <v>4.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.94</v>
+        <v>3.8</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2328,13 +2328,13 @@
         <v>2.1</v>
       </c>
       <c r="M16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.2</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.98</v>
-      </c>
       <c r="O16" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
         <v>2.05</v>
@@ -2349,13 +2349,13 @@
         <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>3.07</v>
+        <v>2.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
@@ -2382,7 +2382,7 @@
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AF16" t="n">
         <v>1.91</v>
@@ -2444,28 +2444,28 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.11</v>
+        <v>2.87</v>
       </c>
       <c r="M17" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="O17" t="n">
         <v>3.54</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
         <v>2.9</v>
@@ -2489,28 +2489,28 @@
         <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.625</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>4.65</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.55</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
         <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="U18" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
         <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>5.23</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="P19" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.77</v>
+        <v>5.76</v>
       </c>
       <c r="R19" t="n">
         <v>1.18</v>
@@ -2706,49 +2706,49 @@
         <v>4.05</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="V19" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="W19" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.94</v>
+        <v>2.24</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>5.23</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="O21" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="P21" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.76</v>
+        <v>4.55</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>4.05</v>
+        <v>3.92</v>
       </c>
       <c r="T21" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.85</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,40 +3158,40 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.3</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>4.17</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="T23" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="U23" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="V23" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
         <v>1.02</v>
@@ -3200,31 +3200,31 @@
         <v>1.14</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>4.36</v>
+        <v>5.11</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="W24" t="n">
         <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.64</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>5.11</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="S25" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="T25" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="V25" t="n">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.06</v>
+        <v>2.49</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46048.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.12</v>
+        <v>4.36</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="U26" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
         <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46048.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
         <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="U27" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="V27" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="AD27" t="n">
         <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="M28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="T28" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="V28" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="AD28" t="n">
         <v>1.17</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46048.70833333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="O31" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q31" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AF31" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46048.70833333334</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="M2" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
         <v>2.88</v>
       </c>
       <c r="O2" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q2" t="n">
         <v>3.3</v>
@@ -683,13 +683,13 @@
         <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V2" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="W2" t="n">
         <v>1.12</v>
@@ -701,31 +701,31 @@
         <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.43</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
         <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46048.15277777778</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AB3" t="n">
         <v>1.4</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
         <v>2.75</v>
       </c>
-      <c r="N6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V6" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AB6" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46048.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46048.41666666666</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="M8" t="n">
         <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
         <v>2.64</v>
@@ -1403,7 +1403,7 @@
         <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
@@ -1412,28 +1412,28 @@
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>3.17</v>
       </c>
       <c r="AA8" t="n">
         <v>2.11</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.89</v>
+        <v>3.35</v>
       </c>
       <c r="AD8" t="n">
         <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
         <v>1.32</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="O10" t="n">
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
         <v>5.75</v>
       </c>
       <c r="R10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.38</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V10" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
         <v>1.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD10" t="n">
         <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.5</v>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O12" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.34</v>
@@ -1906,7 +1906,7 @@
         <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="M13" t="n">
         <v>4.8</v>
@@ -2028,7 +2028,7 @@
         <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AG13" t="n">
         <v>1.2</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="M17" t="n">
         <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
         <v>3.54</v>
@@ -2462,10 +2462,10 @@
         <v>2.62</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>2.87</v>
       </c>
       <c r="T17" t="n">
         <v>2.9</v>
@@ -2474,7 +2474,7 @@
         <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>7.3</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
@@ -2483,7 +2483,7 @@
         <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
         <v>3.1</v>
@@ -2504,13 +2504,13 @@
         <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
         <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.625</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="P18" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>4.35</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="T18" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.55</v>
+        <v>2.21</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="M19" t="n">
-        <v>5.23</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.76</v>
+        <v>4.28</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>4.05</v>
+        <v>3.36</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>4.25</v>
+        <v>5.05</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>4.65</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.01</v>
+        <v>1.89</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.47</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V20" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.21</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.88</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.71</v>
       </c>
       <c r="AE20" t="n">
         <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V21" t="n">
         <v>4.5</v>
       </c>
-      <c r="N21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.33</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.55</v>
+        <v>6.5</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.77</v>
+        <v>5.5</v>
       </c>
       <c r="R22" t="n">
         <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U22" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="V22" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.95</v>
+        <v>5.84</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.94</v>
+        <v>2.24</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>2.64</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O23" t="n">
         <v>3.2</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.33</v>
-      </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.17</v>
+        <v>2.62</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>3.36</v>
+        <v>3.68</v>
       </c>
       <c r="T23" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="U23" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="V23" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X23" t="n">
         <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>5.11</v>
+        <v>4.24</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="W24" t="n">
         <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
         <v>2.9</v>
@@ -3411,16 +3411,16 @@
         <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="R25" t="n">
         <v>1.58</v>
       </c>
       <c r="S25" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="T25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U25" t="n">
         <v>1.22</v>
@@ -3438,7 +3438,7 @@
         <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AA25" t="n">
         <v>2.49</v>
@@ -3450,13 +3450,13 @@
         <v>3.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
         <v>1.4</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="M26" t="n">
         <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>4.36</v>
+        <v>5.15</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>6.07</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="T26" t="n">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="V26" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="W26" t="n">
         <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46048.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N27" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="T27" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="V27" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="AD27" t="n">
         <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
         <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="U28" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="V28" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="AD28" t="n">
         <v>1.17</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3991,34 +3991,34 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
         <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O30" t="n">
         <v>2.7</v>
       </c>
       <c r="P30" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Q30" t="n">
         <v>4.95</v>
       </c>
       <c r="R30" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S30" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="T30" t="n">
         <v>3.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="V30" t="n">
         <v>10.5</v>
@@ -4030,13 +4030,13 @@
         <v>1.08</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Z30" t="n">
         <v>2.43</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AB30" t="n">
         <v>1.39</v>
@@ -4054,7 +4054,7 @@
         <v>1.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
         <v>1.74</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N31" t="n">
-        <v>2.99</v>
+        <v>2.25</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>2.53</v>
+        <v>3.15</v>
       </c>
       <c r="T31" t="n">
-        <v>3.12</v>
+        <v>2.41</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>7.8</v>
+        <v>5.55</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.86</v>
+        <v>4.2</v>
       </c>
       <c r="AA31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB31" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB31" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AC31" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46048.70833333334</v>
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M32" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>8.15</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46048.71875</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O8" t="n">
         <v>2.64</v>
@@ -1409,25 +1409,25 @@
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.17</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.35</v>
+        <v>3.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
         <v>1.97</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.64</v>
+        <v>5.75</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="T9" t="n">
-        <v>3.22</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>2.49</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>5.9</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P10" t="n">
         <v>2</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.08</v>
-      </c>
       <c r="Q10" t="n">
-        <v>5.75</v>
+        <v>2.64</v>
       </c>
       <c r="R10" t="n">
         <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.77</v>
+        <v>3.22</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.49</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.5</v>
@@ -1730,28 +1730,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
         <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
         <v>3.1</v>
@@ -1769,34 +1769,34 @@
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA11" t="n">
         <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC11" t="n">
         <v>4.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
         <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.51388888889</v>
@@ -1977,7 +1977,7 @@
         <v>1.41</v>
       </c>
       <c r="O13" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="P13" t="n">
         <v>2.38</v>
@@ -1992,7 +1992,7 @@
         <v>3.22</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U13" t="n">
         <v>1.51</v>
@@ -2004,7 +2004,7 @@
         <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
         <v>1.19</v>
@@ -2028,7 +2028,7 @@
         <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AG13" t="n">
         <v>1.2</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="P14" t="n">
-        <v>3.26</v>
+        <v>2.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.5</v>
+        <v>6.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1.96</v>
       </c>
-      <c r="U14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.94</v>
+        <v>3.96</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="M15" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="O15" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="P15" t="n">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.9</v>
+        <v>7.14</v>
       </c>
       <c r="R15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.2</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.16</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.55</v>
+        <v>6.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2325,70 +2325,70 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="M16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.1</v>
       </c>
-      <c r="N16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.98</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AF16" t="n">
         <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
         <v>1.62</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V18" t="n">
         <v>4.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.55</v>
       </c>
       <c r="W18" t="n">
         <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.21</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="O19" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.28</v>
+        <v>4.35</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>3.36</v>
+        <v>3.88</v>
       </c>
       <c r="T19" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="V19" t="n">
-        <v>5.05</v>
+        <v>4.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.65</v>
+        <v>5.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.38</v>
+        <v>2.71</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.37</v>
+        <v>2.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,37 +2920,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="M21" t="n">
         <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
         <v>3.68</v>
       </c>
       <c r="T21" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="U21" t="n">
         <v>1.68</v>
       </c>
       <c r="V21" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="W21" t="n">
         <v>1.14</v>
@@ -2959,34 +2959,34 @@
         <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
         <v>5.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB21" t="n">
         <v>2.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>6.5</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="P22" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.5</v>
+        <v>4.28</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.98</v>
+        <v>3.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="U22" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="V22" t="n">
-        <v>4.3</v>
+        <v>5.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.84</v>
+        <v>4.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.64</v>
+        <v>1.42</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>6.5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.62</v>
+        <v>5.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="T23" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="U23" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V23" t="n">
-        <v>4.55</v>
+        <v>4.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.5</v>
+        <v>5.84</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AD23" t="n">
         <v>1.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AF23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH23" t="n">
         <v>2.8</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,37 +3277,37 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="N24" t="n">
-        <v>4.24</v>
+        <v>3.81</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="V24" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
         <v>1.03</v>
@@ -3316,34 +3316,34 @@
         <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.08</v>
+        <v>2.45</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4</v>
+        <v>4.24</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="P25" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.3</v>
+        <v>4.85</v>
       </c>
       <c r="R25" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="U25" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46048.6875</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="N26" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="O26" t="n">
         <v>2.25</v>
@@ -3557,16 +3557,16 @@
         <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD26" t="n">
         <v>1.21</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="O27" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>3.77</v>
       </c>
       <c r="R27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="T28" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="V28" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG28" t="n">
         <v>1.36</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="M30" t="n">
         <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O30" t="n">
         <v>2.7</v>
@@ -4006,7 +4006,7 @@
         <v>1.82</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="R30" t="n">
         <v>1.58</v>
@@ -4015,7 +4015,7 @@
         <v>2.26</v>
       </c>
       <c r="T30" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
         <v>1.2</v>
@@ -4027,19 +4027,19 @@
         <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z30" t="n">
         <v>2.43</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC30" t="n">
         <v>5.7</v>
@@ -4051,7 +4051,7 @@
         <v>2.25</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG30" t="n">
         <v>1.33</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46048.70833333334</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -897,19 +897,19 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M4" t="n">
         <v>4</v>
       </c>
-      <c r="M4" t="n">
-        <v>4.35</v>
-      </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O4" t="n">
-        <v>4.29</v>
+        <v>4.05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
         <v>2.22</v>
@@ -918,13 +918,13 @@
         <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="T4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="V4" t="n">
         <v>3.58</v>
@@ -948,22 +948,22 @@
         <v>3.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AG4" t="n">
         <v>1.18</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46048.35416666666</v>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="N5" t="n">
-        <v>4.49</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q5" t="n">
         <v>4.8</v>
@@ -1037,13 +1037,13 @@
         <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="T5" t="n">
         <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
         <v>6.05</v>
@@ -1055,16 +1055,16 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
         <v>3.98</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC5" t="n">
         <v>2.66</v>
@@ -1082,7 +1082,7 @@
         <v>1.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46048.375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>2.15</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.72</v>
+        <v>6.67</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>2.54</v>
+        <v>2.81</v>
       </c>
       <c r="T8" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>3.49</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.89</v>
+        <v>3.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
         <v>1.97</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46048.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>2.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.75</v>
+        <v>4.72</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.95</v>
+        <v>2.54</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.49</v>
+        <v>1.73</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>5.05</v>
       </c>
       <c r="N12" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>5.13</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>5.15</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.75</v>
+        <v>3.75</v>
       </c>
       <c r="M13" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>6.5</v>
+        <v>4.47</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="R13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.3</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.18</v>
+        <v>2.99</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.26</v>
+        <v>2.16</v>
       </c>
       <c r="O16" t="n">
-        <v>2.76</v>
+        <v>3.39</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
         <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB16" t="n">
         <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
         <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,40 +2444,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="M17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T17" t="n">
         <v>3.1</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
         <v>1.06</v>
@@ -2486,31 +2486,31 @@
         <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
         <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.625</v>
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="P18" t="n">
         <v>2.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
         <v>1.21</v>
@@ -2587,49 +2587,49 @@
         <v>3.68</v>
       </c>
       <c r="T18" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
         <v>5.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
         <v>2.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
         <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.35</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>3.88</v>
+        <v>3.98</v>
       </c>
       <c r="T19" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V19" t="n">
-        <v>4.55</v>
+        <v>4.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="AA19" t="n">
         <v>1.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="O20" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="P20" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="R20" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>4.15</v>
+        <v>3.36</v>
       </c>
       <c r="T20" t="n">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="U20" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>3.68</v>
+        <v>5.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.35</v>
+        <v>4.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.23</v>
+        <v>2.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.64</v>
+        <v>1.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="P21" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.62</v>
+        <v>3.16</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>3.68</v>
+        <v>4.33</v>
       </c>
       <c r="T21" t="n">
-        <v>2.13</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="V21" t="n">
-        <v>4.55</v>
+        <v>3.52</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.63</v>
+        <v>3.46</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.11</v>
+        <v>1.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.8</v>
+        <v>3.28</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>2.95</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.28</v>
+        <v>2.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S22" t="n">
-        <v>3.36</v>
+        <v>3.68</v>
       </c>
       <c r="T22" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="U22" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="V22" t="n">
-        <v>5.05</v>
+        <v>4.55</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.65</v>
+        <v>5.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.96</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="P23" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.5</v>
+        <v>4.35</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S23" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="T23" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V23" t="n">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="W23" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.84</v>
+        <v>5.67</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AC23" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.24</v>
+        <v>2.58</v>
       </c>
       <c r="AG23" t="n">
         <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3399,10 +3399,10 @@
         <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>4.24</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
         <v>2.42</v>
@@ -3420,13 +3420,13 @@
         <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="W25" t="n">
         <v>1.03</v>
@@ -3444,25 +3444,25 @@
         <v>2.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE25" t="n">
         <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG25" t="n">
         <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46048.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,37 +3634,37 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="N27" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P27" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.77</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="S27" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="T27" t="n">
-        <v>3.05</v>
+        <v>3.62</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="V27" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.02</v>
@@ -3673,34 +3673,34 @@
         <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
         <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N28" t="n">
         <v>2.7</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.75</v>
-      </c>
       <c r="O28" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.22</v>
+        <v>3.92</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="T28" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="U28" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="V28" t="n">
-        <v>10.5</v>
+        <v>8.1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG28" t="n">
         <v>1.36</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="S29" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>5.55</v>
+        <v>7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>3.95</v>
+        <v>2.36</v>
       </c>
       <c r="O30" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="P30" t="n">
-        <v>1.82</v>
+        <v>2.21</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.9</v>
+        <v>2.71</v>
       </c>
       <c r="R30" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>2.26</v>
+        <v>3.15</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>2.41</v>
       </c>
       <c r="U30" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>10.5</v>
+        <v>5.55</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.43</v>
+        <v>4.15</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.73</v>
+        <v>1.66</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.7</v>
+        <v>2.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46048.70833333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46048.70833333334</v>
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M32" t="n">
         <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>8.289999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="O32" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="P32" t="n">
         <v>2.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="R32" t="n">
         <v>1.41</v>
@@ -4259,7 +4259,7 @@
         <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="W32" t="n">
         <v>1.04</v>
@@ -4268,16 +4268,16 @@
         <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AA32" t="n">
         <v>2.08</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC32" t="n">
         <v>3.73</v>
@@ -4286,7 +4286,7 @@
         <v>1.24</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="AF32" t="n">
         <v>1.53</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -1466,14 +1466,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Gorica</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Varaždin</t>
-        </is>
-      </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>2.46</v>
+        <v>4.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.72</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="U9" t="n">
         <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
         <v>2.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
         <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.5</v>
@@ -1585,14 +1585,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Varaždin</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Gorica</t>
-        </is>
-      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>4.33</v>
+        <v>2.46</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.64</v>
+        <v>4.72</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="T10" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
         <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
         <v>2.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE10" t="n">
         <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="M12" t="n">
-        <v>5.05</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.4</v>
       </c>
-      <c r="O12" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.52</v>
-      </c>
       <c r="V12" t="n">
-        <v>5.15</v>
+        <v>6.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>5.05</v>
       </c>
       <c r="N13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.85</v>
       </c>
-      <c r="O13" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.58333333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH18" t="n">
         <v>2.8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
         <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>4.35</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V19" t="n">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.65</v>
+        <v>5.67</v>
       </c>
       <c r="AA19" t="n">
         <v>1.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
         <v>1.73</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.24</v>
+        <v>2.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="O23" t="n">
-        <v>2.16</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.35</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S23" t="n">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="T23" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="U23" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="V23" t="n">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.58</v>
+        <v>2.94</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.04</v>
+        <v>1.64</v>
       </c>
       <c r="M24" t="n">
-        <v>2.86</v>
+        <v>3.34</v>
       </c>
       <c r="N24" t="n">
-        <v>3.81</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>6.07</v>
       </c>
       <c r="R24" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="U24" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>7.3</v>
       </c>
       <c r="W24" t="n">
         <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.44</v>
+        <v>1.98</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
         <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.64</v>
+        <v>2.04</v>
       </c>
       <c r="M26" t="n">
-        <v>3.34</v>
+        <v>2.86</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2</v>
+        <v>3.81</v>
       </c>
       <c r="O26" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.07</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S26" t="n">
-        <v>2.47</v>
+        <v>2.24</v>
       </c>
       <c r="T26" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="V26" t="n">
-        <v>7.3</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
         <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG26" t="n">
         <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46048.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>2.71</v>
       </c>
       <c r="R29" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="T29" t="n">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>7</v>
+        <v>5.55</v>
       </c>
       <c r="W29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.03</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.36</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.52</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M30" t="n">
         <v>3</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N30" t="n">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="P30" t="n">
-        <v>2.21</v>
+        <v>1.82</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.71</v>
+        <v>4.95</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="S30" t="n">
-        <v>3.15</v>
+        <v>2.26</v>
       </c>
       <c r="T30" t="n">
-        <v>2.41</v>
+        <v>3.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="V30" t="n">
-        <v>5.55</v>
+        <v>10.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.15</v>
+        <v>2.39</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.66</v>
+        <v>2.73</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.23</v>
+        <v>1.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.67</v>
+        <v>6.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.38</v>
+        <v>1.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46048.70833333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N31" t="n">
         <v>3</v>
       </c>
-      <c r="N31" t="n">
-        <v>4</v>
-      </c>
       <c r="O31" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.95</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="T31" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="V31" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
         <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.39</v>
+        <v>2.86</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="AC31" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46048.70833333334</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -659,37 +659,37 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N2" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="P2" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V2" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="W2" t="n">
         <v>1.12</v>
@@ -698,34 +698,34 @@
         <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>4.61</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AC2" t="n">
         <v>2.51</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AG2" t="n">
         <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46048.15277777778</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>3.87</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1254,37 +1254,37 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.06</v>
+        <v>4.26</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.74</v>
+        <v>3.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="V7" t="n">
-        <v>9.9</v>
+        <v>15</v>
       </c>
       <c r="W7" t="n">
         <v>1.02</v>
@@ -1293,34 +1293,34 @@
         <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.05</v>
+        <v>6.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46048.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.67</v>
+        <v>4.72</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.81</v>
+        <v>2.54</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.49</v>
+        <v>2.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46048.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="O9" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.64</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="T9" t="n">
-        <v>3.22</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>2.49</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.5</v>
@@ -1585,14 +1585,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Gorica</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Varaždin</t>
-        </is>
-      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>2.46</v>
+        <v>4.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.72</v>
+        <v>2.64</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="U10" t="n">
         <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
         <v>2.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
         <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="N14" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="P14" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.9</v>
+        <v>7.14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="V14" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.55</v>
+        <v>6.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.96</v>
+        <v>5.25</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="N15" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="P15" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="U15" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V15" t="n">
-        <v>3.72</v>
+        <v>4.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.8</v>
+        <v>6.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.25</v>
+        <v>3.96</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.99</v>
+        <v>2.18</v>
       </c>
       <c r="M16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.1</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.98</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
         <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
         <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
         <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46048.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.18</v>
+        <v>2.87</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.26</v>
+        <v>2.44</v>
       </c>
       <c r="O17" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46048.625</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.4</v>
       </c>
-      <c r="M18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="AB18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.7</v>
       </c>
-      <c r="V18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.24</v>
+        <v>2.94</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.8</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>3.92</v>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="O19" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="P19" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.35</v>
+        <v>3.55</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>3.36</v>
       </c>
       <c r="T19" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="U19" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>4.55</v>
+        <v>5.05</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.67</v>
+        <v>4.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.71</v>
+        <v>2.35</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.58</v>
+        <v>2.37</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="M20" t="n">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="N20" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.55</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="S20" t="n">
-        <v>3.36</v>
+        <v>4.33</v>
       </c>
       <c r="T20" t="n">
-        <v>2.29</v>
+        <v>1.87</v>
       </c>
       <c r="U20" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="V20" t="n">
-        <v>5.05</v>
+        <v>3.52</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.6</v>
+        <v>6.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.35</v>
+        <v>3.46</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>2.06</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.37</v>
+        <v>3.28</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="O21" t="n">
-        <v>2.26</v>
+        <v>1.75</v>
       </c>
       <c r="P21" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.16</v>
+        <v>5.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="T21" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="U21" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="V21" t="n">
-        <v>3.52</v>
+        <v>4.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.75</v>
+        <v>5.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.46</v>
+        <v>2.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.28</v>
+        <v>2.24</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.88</v>
+        <v>2.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,34 +3039,34 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="M22" t="n">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.62</v>
+        <v>4.35</v>
       </c>
       <c r="R22" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S22" t="n">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="U22" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V22" t="n">
         <v>4.55</v>
@@ -3075,37 +3075,37 @@
         <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.7</v>
+        <v>5.67</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,22 +3158,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="N23" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R23" t="n">
         <v>1.21</v>
@@ -3182,16 +3182,16 @@
         <v>3.68</v>
       </c>
       <c r="T23" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="U23" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="V23" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="W23" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X23" t="n">
         <v>1.02</v>
@@ -3200,31 +3200,31 @@
         <v>1.13</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3396,31 +3396,31 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="M25" t="n">
         <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>4.38</v>
       </c>
       <c r="O25" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="P25" t="n">
         <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>3.11</v>
+        <v>2.94</v>
       </c>
       <c r="U25" t="n">
         <v>1.35</v>
@@ -3441,28 +3441,28 @@
         <v>3.08</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC25" t="n">
         <v>3.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE25" t="n">
         <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46048.6875</v>
@@ -3634,52 +3634,52 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="M27" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="O27" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="S27" t="n">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="T27" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="U27" t="n">
         <v>1.24</v>
       </c>
       <c r="V27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="Z27" t="n">
         <v>2.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AB27" t="n">
         <v>1.56</v>
@@ -3688,16 +3688,16 @@
         <v>4.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AH27" t="n">
         <v>1.44</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="M30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" t="n">
-        <v>4</v>
-      </c>
       <c r="O30" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.95</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="S30" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="U30" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
         <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.39</v>
+        <v>2.86</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46048.70833333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>4.95</v>
       </c>
       <c r="R31" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="S31" t="n">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="T31" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.86</v>
+        <v>2.39</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.73</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46048.70833333334</v>
@@ -4229,31 +4229,31 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="M32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="N32" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="O32" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="P32" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.5</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="U32" t="n">
         <v>1.35</v>
@@ -4268,34 +4268,34 @@
         <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AA32" t="n">
         <v>2.08</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46048.71875</v>

--- a/jogos_2026-01-26.xlsx
+++ b/jogos_2026-01-26.xlsx
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="M4" t="n">
         <v>4</v>
@@ -906,25 +906,25 @@
         <v>1.7</v>
       </c>
       <c r="O4" t="n">
-        <v>4.05</v>
+        <v>4.39</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="T4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.89</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.86</v>
       </c>
       <c r="V4" t="n">
         <v>3.58</v>
@@ -939,19 +939,19 @@
         <v>1.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AE4" t="n">
         <v>1.33</v>
@@ -960,10 +960,10 @@
         <v>3</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46048.35416666666</v>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="P5" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
         <v>4.8</v>
@@ -1040,7 +1040,7 @@
         <v>3.04</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="U5" t="n">
         <v>1.44</v>
@@ -1055,7 +1055,7 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
         <v>3.98</v>
@@ -1064,25 +1064,25 @@
         <v>1.68</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC5" t="n">
         <v>2.66</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AE5" t="n">
         <v>1.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46048.375</v>
@@ -1347,14 +1347,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Gorica</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Varaždin</t>
-        </is>
-      </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.46</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.72</v>
+        <v>2.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="U8" t="n">
         <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
         <v>2.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
         <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46048.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>2.88</v>
       </c>
       <c r="M9" t="n">
-        <v>3.98</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>5.3</v>
+        <v>2.38</v>
       </c>
       <c r="O9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.23</v>
-      </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>2.81</v>
+        <v>2.54</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.49</v>
+        <v>1.73</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46048.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>6.9</v>
       </c>
       <c r="O10" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.64</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
         <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>3.22</v>
+        <v>2.69</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.45</v>
+        <v>2.97</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46048.5</v>
@@ -1730,46 +1730,46 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
         <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
         <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
         <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W11" t="n">
         <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="Z11" t="n">
         <v>2.74</v>
@@ -1778,25 +1778,25 @@
         <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
         <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46048.51388888889</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.75</v>
+        <v>7.33</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="O12" t="n">
-        <v>4.47</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AB12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46048.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="M13" t="n">
-        <v>5.05</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="O13" t="n">
-        <v>5.13</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.77</v>
+        <v>2.37</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>5.15</v>
+        <v>6.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46048.58333333334</v>
@@ -2093,67 +2093,67 @@
         <v>7.4</v>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.14</v>
+        <v>10</v>
       </c>
       <c r="R14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="U14" t="n">
         <v>1.79</v>
       </c>
       <c r="V14" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
         <v>1.04</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2206,31 +2206,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="M15" t="n">
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="N15" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.91</v>
+        <v>2.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="R15" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S15" t="n">
         <v>4.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="U15" t="n">
         <v>1.75</v>
@@ -2239,40 +2239,40 @@
         <v>4.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
         <v>6.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.96</v>
+        <v>3.27</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46048.60416666666</v>
@@ -2325,70 +2325,70 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
         <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
         <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
         <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
         <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
         <v>1.62</v>
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="M17" t="n">
         <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P17" t="n">
         <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
@@ -2501,13 +2501,13 @@
         <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
         <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AH17" t="n">
         <v>1.36</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>2.63</v>
+        <v>2.21</v>
       </c>
       <c r="P18" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.68</v>
+        <v>3.36</v>
       </c>
       <c r="T18" t="n">
-        <v>2.04</v>
+        <v>2.29</v>
       </c>
       <c r="U18" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="V18" t="n">
-        <v>4.45</v>
+        <v>5.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.94</v>
+        <v>2.37</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.92</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>3.36</v>
+        <v>3.98</v>
       </c>
       <c r="T19" t="n">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.57</v>
       </c>
-      <c r="V19" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AF19" t="n">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="O20" t="n">
-        <v>2.26</v>
+        <v>2.63</v>
       </c>
       <c r="P20" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="T20" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="U20" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="V20" t="n">
-        <v>3.52</v>
+        <v>4.45</v>
       </c>
       <c r="W20" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.46</v>
+        <v>2.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.28</v>
+        <v>2.94</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46048.66666666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="M21" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="P21" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.5</v>
+        <v>3.16</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="T21" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="V21" t="n">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.65</v>
+        <v>6.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.85</v>
+        <v>3.46</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.24</v>
+        <v>3.28</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.8</v>
+        <v>1.88</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,34 +3039,34 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.67</v>
+        <v>2.95</v>
       </c>
       <c r="M22" t="n">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.35</v>
+        <v>2.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="T22" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="U22" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V22" t="n">
         <v>4.55</v>
@@ -3075,37 +3075,37 @@
         <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.67</v>
+        <v>5.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,34 +3158,34 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="P23" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.62</v>
+        <v>4.35</v>
       </c>
       <c r="R23" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S23" t="n">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="T23" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="U23" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V23" t="n">
         <v>4.55</v>
@@ -3194,37 +3194,37 @@
         <v>1.14</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.7</v>
+        <v>5.67</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46048.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="M24" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.07</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
-        <v>2.47</v>
+        <v>2.24</v>
       </c>
       <c r="T24" t="n">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="V24" t="n">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AF24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46048.6875</v>
@@ -3396,16 +3396,16 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="P25" t="n">
         <v>2.06</v>
@@ -3414,19 +3414,19 @@
         <v>4.9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="T25" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
         <v>1.35</v>
       </c>
       <c r="V25" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.03</v>
@@ -3444,7 +3444,7 @@
         <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
         <v>3.8</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="M26" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.81</v>
+        <v>5.2</v>
       </c>
       <c r="O26" t="n">
-        <v>2.63</v>
+        <v>2.17</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="T26" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="U26" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>10</v>
+        <v>7.3</v>
       </c>
       <c r="W26" t="n">
         <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH26" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.67</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46048.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.86</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="N27" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>3.92</v>
       </c>
       <c r="R27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V27" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.59</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V27" t="n">
-        <v>10</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AC27" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AD27" t="n">
         <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="S28" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="T28" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="U28" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="V28" t="n">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.85</v>
+        <v>2.61</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="AD28" t="n">
         <v>1.17</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46048.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O29" t="n">
         <v>3</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.45</v>
-      </c>
       <c r="P29" t="n">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="S29" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="T29" t="n">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="V29" t="n">
-        <v>5.55</v>
+        <v>7.9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46048.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>5.23</v>
       </c>
       <c r="R30" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>2.23</v>
       </c>
       <c r="T30" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
       <c r="AB30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.74</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.52</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46048.70833333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.09</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="O31" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="P31" t="n">
-        <v>1.82</v>
+        <v>2.21</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.95</v>
+        <v>2.71</v>
       </c>
       <c r="R31" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>2.26</v>
+        <v>3.15</v>
       </c>
       <c r="T31" t="n">
-        <v>3.75</v>
+        <v>2.41</v>
       </c>
       <c r="U31" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>10.5</v>
+        <v>5.55</v>
       </c>
       <c r="W31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.03</v>
       </c>
-      <c 